--- a/data/sake-master-v6-dynamic-id.xlsx
+++ b/data/sake-master-v6-dynamic-id.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\清酒網站素材\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{832ACB55-6BAF-4181-9F44-437D525D914A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8593B475-845E-496F-82F2-63C3A06BABE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="1800" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="酒款主資料" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3949" uniqueCount="1356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4119" uniqueCount="1454">
   <si>
     <t>酒款ID</t>
   </si>
@@ -4554,14 +4554,6 @@
   </si>
   <si>
     <t>微氣泡、可爾必思、酸度柔和、尾韻微苦</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>輕快與豐潤的口感多汁且爽口，微濁酒可以喝到一半在搖晃混合，口感更為圓潤</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>清爽的酸度配上氣泡，未過濾未殺菌清酒特有的多汁口感，但並不厚重</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
@@ -4659,14 +4651,6 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>入口酒精感偏突出；回溫後甜感上升，表現比神宴一農更好，酒精感相對弱化，尾段帶些微苦味。</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>入口酒精感偏突出；回溫後甜感上升，酒精感相對弱化，尾段帶些微苦味。</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>入口圓潤酒體厚實、糖蜜、微氣泡</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
@@ -4718,34 +4702,6 @@
   </si>
   <si>
     <t>水梨、乳酸香、淡香蕉調</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>細緻氣泡、輕盈清爽，帶柔滑微稠質地；旨味、甜味柔和，果酸明亮，尾段微苦</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>強氣泡、輕快清澈、礦物感、乾淨旨甜、俐落酸、微苦</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>強氣泡，比起四農增穗口感多了更多鮮味，非常甜美但不死甜</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>細緻氣泡、濃厚旨甜、微稠、礦物與萃取感、高酸微澀、柔順且具野性複雜度</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>細緻氣泡、旨味厚實、高酸、微澀、吞嚥下去木桶香氣會返回</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>細緻氣泡，中段有柔和的旨味、甜味與穀物感；質地細緻、不會像七農那麼厚</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>強氣泡，輕快但帶一點奶油般的柔軟感；米旨味、甜味與些許黏稠感，酸度俐落</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
@@ -5094,10 +5050,6 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>細緻氣泡＋滑順、絲綢感，旨味、甜味、萃取感都高，酸、微苦、微澀把輪廓收住</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>暢飲活動12+1</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
@@ -5734,10 +5686,6 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>米甜、鮮明酸度、微澀、茶感</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>淡淡果香、米香</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
@@ -5779,57 +5727,6 @@
   </si>
   <si>
     <t>入口質地細膩輕盈，酒體純淨通透。收尾極為乾脆俐落，酒精感隱藏得很好，後味沒有黏膩感。</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF253041"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>香氣華麗，入口清爽果味與米甜交錯，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF253041"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>酸度的表現很好不會讓這支酒過於甜膩</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF253041"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF253041"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>尾韻留下茶味的餘韻，喝起來非常舒服讓人一杯接一杯</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF253041"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>。</t>
-    </r>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
@@ -6083,15 +5980,1066 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>紮實飽滿的酒感，甜味優雅，讓酒液在嘴裡待一下果酸平衡了整體的甜潤感，尾韻帶有柔和悠長的米旨味，最後有微微的酒精辛辣感收尾。</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>T00051</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>入口就是滿滿的鮮味與米旨味，</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>S0210</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>清爽的酸度配上氣泡，未過濾未殺菌清酒特有的多汁口感，但並不厚重。</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>輕快與豐潤的口感多汁且爽口，微濁酒可以喝到一半在搖晃混合，口感更為圓潤。</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>淡淡木質香與氣泡，回溫後甜感上升比神宴一農更為突出，酒精感相對弱化，尾段帶些微苦味。</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>入口酒精感偏突出微氣泡；香氣相較內斂，回溫後甜感上升酒精感相對弱化，這時候喝比剛開時好喝，尾韻帶些微微苦味。</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>細緻氣泡輕盈清爽，帶柔滑微稠質地；旨味、甜味柔和，果酸明亮，尾段微苦。</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>非常活潑的氣泡，奔放的香氣入口酸甜帶點礦物感，香氣帶點野性的味道(很特殊的味道)，尾韻俐落微苦的味道做漂亮的收尾。</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>非常活潑的氣泡，整體比起四農增穗多了更多鮮味，味道非常飽與甜味與酸味都被放大不死甜，配上活潑的氣泡讚，收尾一樣乾淨俐落。</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>非常奔放的香氣聞了會餓的那種，入口是活潑的碳酸氣泡感味道帶一點奶油般的柔軟感；米旨味與甜味交合再一起，配上些許黏稠的口感與俐落酸度，最後吞嚥時微微的苦味增加了層次。</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>香氣相較四農較為收斂，氣泡較細緻優雅，酸度提高旨味變得更為厚實，野性的感覺更強，吞嚥下去後木桶氣香氣隨之回湧，餘韻綿長且富有層次。</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>氣泡細緻優雅，原本的酸味與酸度轉換為接近優格的香氣與口感，整體更為柔和，品嘗時會冒出一種像稻草與雨後泥土的自然氣息，很耐喝味道一層一層的。</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>氣泡溫和不扎口，乳酸的味道和口感更突出了。跟四農奔放的香氣比，六農變得沉穩、很有氣質。入喉超順，而且最後留在嘴巴裡的米香和穀物香氣很有存在感。</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>七農的氣泡雖然很細、口感像絲綢一樣滑順，旨味和甜感也真的超級飽滿，但我個人覺得它偏甜了一點，喝起來質地更為濃稠，很像糖蜜或蜂蜜的口感。雖然尾韻有酸度和微苦澀把輪廓收住，但相較之下，我其實更喜歡六農那種內斂高雅、穀物感明顯的平衡感。</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>這支喝起來蠻有份量的，一入口甜得很順、很舒服，但含一下那個果酸就跳出來，完全不會死甜。吞下去之後嘴裡都是米香，最後喉嚨帶一點點酒感收尾，很過癮。</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Philly Sour Prototype</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>S0211</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>仙禽</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>線香花火</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>純米吟醸</t>
+    </r>
+  </si>
+  <si>
+    <t>仙禽酒造</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>山田錦：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>66%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> 雄町：34%</t>
+    </r>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>十四代</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>吟撰吟釀</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>高木酒造</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>大吟釀</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>兵庫縣產特A山田錦</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>S0212</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>S0213</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>荷札酒</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>加茂錦酒造</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>美鄉錦</t>
+  </si>
+  <si>
+    <r>
+      <t>美鄉錦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>しぼりたで</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>初榨純米大吟釀</t>
+    </r>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>開瓶是很討喜的果香。入口先嚐到清爽的果甜與淡淡米香，微酸的口感把甜度平衡得剛剛好，完全不膩口。最喜歡它吞下後留在嘴裡像茶一樣的回甘，非常順口耐喝，是會讓人不知不覺一杯接一杯的舒服好酒。</t>
+  </si>
+  <si>
+    <t>樂器正宗</t>
+  </si>
+  <si>
+    <t>S0214</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>大木代吉本店</t>
+  </si>
+  <si>
+    <t>FUZZY GREEN 本釀造</t>
+  </si>
+  <si>
+    <t>混釀 愛山</t>
+  </si>
+  <si>
+    <t>S0216</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>S0217</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>S0218</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>S0219</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>ESHIKOTO</t>
+  </si>
+  <si>
+    <t>水鏡 AWA 2020</t>
+  </si>
+  <si>
+    <t>黑龍酒造</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>福井</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>AWA 2023 Pearl ● Pasteurized</t>
+  </si>
+  <si>
+    <t>五百万石 純米大吟醸</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>さかほまれ 特別純米</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>大吟醸さかほまれ雫酒</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>三宅彦右衛門酒造</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>早瀬浦</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>福井產 さかほまれ</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>特別栽培米</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>美山錦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve"> VINTAGE2025</t>
+    </r>
+  </si>
+  <si>
+    <t>常山酒造</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FOMALHAUT 2024 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>火入</t>
+    </r>
+  </si>
+  <si>
+    <t>永平寺白龍</t>
+  </si>
+  <si>
+    <t>純米吟醸 DRAGONWATER</t>
+  </si>
+  <si>
+    <t>EDGE</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>TOAST</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>真</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>永平寺白龍</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>白龍禪 生原酒</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>吉田酒造</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>吉峯蔵</t>
+  </si>
+  <si>
+    <t>純米吟釀 生原酒</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>葵酒造</t>
+  </si>
+  <si>
+    <t>Maison Aoi</t>
+  </si>
+  <si>
+    <t>新保 薄濁</t>
+  </si>
+  <si>
+    <t>萬乘釀造</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>愛知</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>協田 2025</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>涅槃龜</t>
+  </si>
+  <si>
+    <t>低精白 純米酒</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>秋田酒こまち</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>白桃、哈密瓜、紅蘋果、鳳梨</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>芳醇甘口、透明感、果汁感</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>白桃跟哈密瓜香氣超明顯，喝起來微甜又像水一樣順，尾韻乾淨不膩，但回溫後會過於甜膩，還是適合冰冰的喝。</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>荔枝、麝香葡萄、啤酒花香、微柑橘、淡淡米穀香</t>
+  </si>
+  <si>
+    <t>清爽微酸、尾韻微苦、甘苦平衡、酒體輕盈、透明感佳</t>
+  </si>
+  <si>
+    <r>
+      <t>加了京都啤酒花與</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 90% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>低精米山田錦釀成的新派交酒，酒質卻意外清澈不雜。聞起來是明顯的麝香葡萄與清爽草本香；入口先有溫和的米甜味，隨即轉為活潑果酸與啤酒花的淡淡微苦，把尾韻收得很乾淨。喝起來很有清爽型白酒的感覺，酒感輕盈、冰鎮喝很棒。</t>
+    </r>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>青葡萄、蘋果、哈密瓜、米香</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑順細緻、透明感、清爽果酸、米旨味、尾韻微苦</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>聞起來是清爽的青葡萄、蘋果香跟淡淡米香，不會太濃。入口很順、很乾淨，前段微甜帶點果酸，後面有米的甘甜，尾韻帶一點點微苦把味道收得很俐落，耐喝不膩，配海鮮很讚。</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>水梨、草莓奶昔、淡淡白花香、微杏仁堅果香、清爽果香</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>聞起來有明顯的水梨、草莓甜香與淡淡花香</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。入口圓潤，前段是飽滿的甜味配上一波很活潑的果酸，後面帶一點點微鹹與微苦感把味道收乾，酸甜平衡、低酒感超順口</t>
+    </r>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>酸甜感、質地圓潤微稠、尾韻微苦</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>青蘋果、淡淡米香</t>
+  </si>
+  <si>
+    <t>超辛口、完全不甜、後段辛辣感明顯、收尾乾爽</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>聞起來是清爽的青蘋果香，完全不刺鼻。雖然是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> +18 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>超辛口，但入口跟水一樣順，中後段收尾則像武士刀一樣乾淨俐落、完全不甜不拖泥帶水，配重口味的食物超爽快。</t>
+    </r>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>哈密瓜、水梨、米香、熟成果香</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>圓潤滑順、米甘味厚實、尾韻微苦</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>冬天釀好後在酒廠低溫熟成一個夏天才出廠的秋季限定酒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。聞起來有哈密瓜、水梨般的熟成果香跟米香</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>；入口很圓潤滑順，米本身的甘甜味很厚實，尾段帶一點點微苦把味道收乾，有存在感但不會重膩。</t>
+    </r>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>淡淡米香、穀物香、微果香</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>輕快順口、自然米甜、收尾乾淨</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>清爽柑橘香、新鮮果香、微甜米香</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>微氣泡、酒體圓潤、溫和果酸、清爽多汁</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>水梨、白葡萄、草莓果香</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>微甜帶果酸、米</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>旨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>味、收尾俐落</t>
+    </r>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>日常耐喝的基本款，酒精度只有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 14 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。聞起來是低調舒服的米香與淡淡果香</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>；喝起來酒感很輕快，米的甘甜味自然圓潤，尾韻乾淨不拖泥帶水。</t>
+    </r>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>新鮮生酒版本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。聞起來比一般純米酒多了清爽的柑橘系果香；入口有生酒特有的新鮮活力感</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>與氣泡感</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，圓潤的米甜味跟溫和的果酸融合得很好，比常規純米酒更鮮甜多汁，冰鎮喝非常清爽開胃。</t>
+    </r>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>聞起來有水梨、白葡萄與淡淡花果香，香氣比純米系列明顯許多</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。入口輕快乾淨，前段是討喜的微甜與清爽果酸，中後段有柔和的米甘味，收尾俐落不甜膩，是支標準好喝、誰都能輕鬆入口的清爽果香系清酒。</t>
+    </r>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>青蘋果、水梨甜香、濃郁果香</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>甜潤飽滿、無苦澀雜味、蘋果果酸</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>用高速離心機無壓力甩出來的「未加水、未殺菌」生原酒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。聞起來果香超濃郁，是滿滿的青蘋果與水梨甜香</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>；因為是沒兌水稀釋的原酒，入口甜味跟米的濃郁度是全系列最強的，但靠著離心技術完全沒有壓榨的雜味，搭配活潑果酸，濃郁卻超乾淨。</t>
+    </r>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>華麗果香、乳酸、甜潤米香</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>絲綢</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>般滑順</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、無粗糙米渣感、綿密、微甜</t>
+    </r>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>酒標上直接號稱「究極的濁酒」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。一般濁酒喝起來常有粗粗的米渣感，但這支是用離心機甩出來的，質地像絲綢跟牛奶一樣滑順細緻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>！聞起來卻有純米吟釀等級的華麗果香，入口是綿密溫柔的米甜味，尾韻卻收得意外清爽不糊口，徹底顛覆對傳統濁酒的印象。</t>
+    </r>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>清新果香、青蘋果、梨子</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>微薄濁、極致滑順無雜味、溫柔甘甜</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>離心機系列的春季生酒版（帶有一點點微薄濁感），酒精度降到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 15 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>度比生原酒更好入口</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。一開瓶就有奔放的水果香氣，入口是輕柔的果甜味與薄濁酒特有的一點點甘醇感，因為離心取酒完全沒有苦澀味，喝起來比第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>支「生原酒」更水潤輕盈、超順口。</t>
+    </r>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>熟成果香、青蘋果、柔和吟釀香</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>絲綢般滑順、甘甜、微酸</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>把離心機甩出來的純米吟釀，放進酒窖低溫熟成一個夏天的秋季限定版。聞起來是溫和舒服的熟成果香</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF253041"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>；比起春季生酒的奔放，這支經過夏天熟成後把稜角全磨平了，入口像絲絨一樣圓潤滑順，甘甜味跟溫和酸度揉合得剛剛好，是遠心分離系列裡最溫柔耐喝的一支。</t>
+    </r>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -6353,7 +7301,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -6565,14 +7513,26 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6582,7 +7542,6 @@
   <dxfs count="3">
     <dxf>
       <font>
-        <b/>
         <color rgb="FF9B1C1C"/>
       </font>
       <fill>
@@ -6603,6 +7562,7 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
         <color rgb="FF9B1C1C"/>
       </font>
       <fill>
@@ -6625,7 +7585,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SakesV5" displayName="SakesV5" ref="A1:K212" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SakesV5" displayName="SakesV5" ref="A1:K265" totalsRowShown="0">
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="酒款ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="銘柄"/>
@@ -6876,7 +7836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K209"/>
+  <dimension ref="A1:K262"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -7081,7 +8041,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="D7" s="29" t="s">
         <v>31</v>
@@ -9511,7 +10471,7 @@
         <v>368</v>
       </c>
       <c r="B98" s="42" t="s">
-        <v>1267</v>
+        <v>1255</v>
       </c>
       <c r="C98" s="29" t="s">
         <v>369</v>
@@ -9913,7 +10873,7 @@
         <v>417</v>
       </c>
       <c r="B112" s="42" t="s">
-        <v>1269</v>
+        <v>1257</v>
       </c>
       <c r="C112" s="29" t="s">
         <v>419</v>
@@ -12506,13 +13466,13 @@
     </row>
     <row r="208" spans="1:11" s="29" customFormat="1" ht="28.5" customHeight="1">
       <c r="A208" s="29" t="s">
-        <v>1272</v>
+        <v>1260</v>
       </c>
       <c r="B208" s="29" t="s">
-        <v>1270</v>
+        <v>1258</v>
       </c>
       <c r="C208" s="29" t="s">
-        <v>1273</v>
+        <v>1261</v>
       </c>
       <c r="D208" s="29" t="s">
         <v>31</v>
@@ -12525,15 +13485,15 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="209" spans="1:8" s="29" customFormat="1" ht="28.5" customHeight="1">
+    <row r="209" spans="1:11" s="29" customFormat="1" ht="28.5" customHeight="1">
       <c r="A209" s="29" t="s">
-        <v>1286</v>
+        <v>1274</v>
       </c>
       <c r="B209" s="29" t="s">
         <v>671</v>
       </c>
       <c r="C209" s="42" t="s">
-        <v>1287</v>
+        <v>1275</v>
       </c>
       <c r="D209" s="29" t="s">
         <v>673</v>
@@ -12542,9 +13502,744 @@
         <v>85</v>
       </c>
       <c r="F209" s="29" t="s">
-        <v>1288</v>
+        <v>1276</v>
       </c>
       <c r="H209" s="42"/>
+    </row>
+    <row r="210" spans="1:11" s="29" customFormat="1" ht="43.5" customHeight="1">
+      <c r="A210" s="29" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B210" s="42" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C210" s="43" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D210" s="42" t="s">
+        <v>1359</v>
+      </c>
+      <c r="E210" s="43" t="s">
+        <v>432</v>
+      </c>
+      <c r="F210" s="73" t="s">
+        <v>722</v>
+      </c>
+      <c r="G210" s="38" t="s">
+        <v>1360</v>
+      </c>
+      <c r="H210" s="31"/>
+    </row>
+    <row r="211" spans="1:11" s="29" customFormat="1" ht="42" customHeight="1">
+      <c r="A211" s="29" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B211" s="29" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C211" s="43" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D211" s="43" t="s">
+        <v>1363</v>
+      </c>
+      <c r="E211" s="43" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F211" s="29" t="s">
+        <v>1364</v>
+      </c>
+      <c r="G211" s="42" t="s">
+        <v>1365</v>
+      </c>
+      <c r="H211" s="44">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="A212" s="29" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B212" s="29" t="s">
+        <v>356</v>
+      </c>
+      <c r="C212" s="29" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D212" s="29" t="s">
+        <v>358</v>
+      </c>
+      <c r="E212" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="F212" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="H212" s="31">
+        <v>0.9</v>
+      </c>
+      <c r="J212" s="29" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="A213" s="29" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B213" s="37" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C213" s="43" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D213" s="29" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E213" s="43" t="s">
+        <v>85</v>
+      </c>
+      <c r="F213" s="73" t="s">
+        <v>15</v>
+      </c>
+      <c r="G213" s="43" t="s">
+        <v>1370</v>
+      </c>
+      <c r="H213" s="31">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="A214" s="29" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B214" s="43" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C214" s="43" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D214" s="43" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E214" s="43" t="s">
+        <v>401</v>
+      </c>
+      <c r="F214" s="73" t="s">
+        <v>198</v>
+      </c>
+      <c r="G214" s="43"/>
+      <c r="H214" s="31"/>
+    </row>
+    <row r="215" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="A215" s="29" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B215" s="43" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C215" s="43" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D215" s="43" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E215" s="43" t="s">
+        <v>401</v>
+      </c>
+      <c r="F215" s="73" t="s">
+        <v>19</v>
+      </c>
+      <c r="G215" s="43"/>
+      <c r="H215" s="31"/>
+    </row>
+    <row r="216" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="A216" s="29" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B216" s="43" t="s">
+        <v>116</v>
+      </c>
+      <c r="C216" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="D216" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="E216" s="43" t="s">
+        <v>421</v>
+      </c>
+      <c r="F216" s="73"/>
+      <c r="G216" s="43"/>
+      <c r="H216" s="31"/>
+    </row>
+    <row r="217" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="A217" s="29" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B217" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="C217" s="43" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D217" s="43" t="s">
+        <v>1409</v>
+      </c>
+      <c r="E217" s="43" t="s">
+        <v>1410</v>
+      </c>
+      <c r="F217" s="73" t="s">
+        <v>15</v>
+      </c>
+      <c r="G217" s="43" t="s">
+        <v>75</v>
+      </c>
+      <c r="H217" s="31">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11" ht="36" customHeight="1">
+      <c r="A218" s="29" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B218" s="43" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C218" s="43" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D218" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="E218" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="F218" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="G218" s="30" t="s">
+        <v>1414</v>
+      </c>
+      <c r="H218" s="31">
+        <v>0.8</v>
+      </c>
+      <c r="I218" s="30"/>
+      <c r="J218" s="30"/>
+      <c r="K218" s="30"/>
+    </row>
+    <row r="219" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B219" s="43"/>
+      <c r="C219" s="43"/>
+      <c r="D219" s="43"/>
+      <c r="E219" s="43"/>
+      <c r="F219" s="73"/>
+      <c r="G219" s="43"/>
+      <c r="H219" s="31"/>
+    </row>
+    <row r="220" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B220" s="43"/>
+      <c r="C220" s="43"/>
+      <c r="D220" s="43"/>
+      <c r="E220" s="43"/>
+      <c r="F220" s="73"/>
+      <c r="G220" s="43"/>
+      <c r="H220" s="31"/>
+    </row>
+    <row r="221" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="C221" s="43"/>
+      <c r="D221" s="42"/>
+      <c r="F221" s="30"/>
+      <c r="G221" s="30"/>
+      <c r="H221" s="31"/>
+    </row>
+    <row r="222" spans="1:11" ht="36" customHeight="1">
+      <c r="A222" s="29"/>
+      <c r="B222" s="29"/>
+      <c r="C222" s="29"/>
+      <c r="D222" s="29"/>
+      <c r="E222" s="29"/>
+      <c r="F222" s="30"/>
+      <c r="G222" s="30"/>
+      <c r="H222" s="30"/>
+      <c r="I222" s="30"/>
+      <c r="J222" s="30"/>
+      <c r="K222" s="30"/>
+    </row>
+    <row r="223" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B223" s="43"/>
+      <c r="C223" s="43"/>
+      <c r="D223" s="42"/>
+      <c r="F223" s="30"/>
+      <c r="G223" s="30"/>
+      <c r="H223" s="31"/>
+    </row>
+    <row r="224" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B224" s="43"/>
+      <c r="C224" s="43"/>
+      <c r="D224" s="42"/>
+      <c r="F224" s="30"/>
+      <c r="G224" s="30"/>
+      <c r="H224" s="31"/>
+    </row>
+    <row r="225" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B225" s="43"/>
+      <c r="C225" s="43"/>
+      <c r="D225" s="42"/>
+      <c r="F225" s="30"/>
+      <c r="G225" s="30"/>
+      <c r="H225" s="31"/>
+    </row>
+    <row r="226" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B226" s="43"/>
+      <c r="C226" s="43"/>
+      <c r="D226" s="42"/>
+      <c r="F226" s="30"/>
+      <c r="G226" s="30"/>
+      <c r="H226" s="31"/>
+    </row>
+    <row r="227" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B227" s="43"/>
+      <c r="C227" s="43"/>
+      <c r="D227" s="42"/>
+      <c r="F227" s="30"/>
+      <c r="G227" s="30"/>
+      <c r="H227" s="31"/>
+    </row>
+    <row r="228" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B228" s="43"/>
+      <c r="C228" s="43"/>
+      <c r="D228" s="42"/>
+      <c r="F228" s="30"/>
+      <c r="G228" s="30"/>
+      <c r="H228" s="31"/>
+    </row>
+    <row r="229" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B229" s="43"/>
+      <c r="C229" s="43"/>
+      <c r="D229" s="42"/>
+      <c r="F229" s="30"/>
+      <c r="G229" s="30"/>
+      <c r="H229" s="31"/>
+    </row>
+    <row r="230" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B230" s="43"/>
+      <c r="C230" s="43"/>
+      <c r="D230" s="42"/>
+      <c r="F230" s="30"/>
+      <c r="G230" s="30"/>
+      <c r="H230" s="31"/>
+    </row>
+    <row r="231" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B231" s="43"/>
+      <c r="C231" s="43"/>
+      <c r="D231" s="42"/>
+      <c r="F231" s="30"/>
+      <c r="G231" s="30"/>
+      <c r="H231" s="31"/>
+    </row>
+    <row r="232" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B232" s="43"/>
+      <c r="C232" s="43"/>
+      <c r="D232" s="42"/>
+      <c r="E232" s="43"/>
+      <c r="F232" s="30"/>
+      <c r="G232" s="30"/>
+      <c r="H232" s="31"/>
+    </row>
+    <row r="233" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B233" s="43" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C233" s="43" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D233" s="43" t="s">
+        <v>1384</v>
+      </c>
+      <c r="E233" s="43" t="s">
+        <v>1385</v>
+      </c>
+      <c r="F233" s="73"/>
+      <c r="G233" s="43"/>
+      <c r="H233" s="31"/>
+    </row>
+    <row r="234" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B234" s="43" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C234" s="43" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D234" s="43" t="s">
+        <v>1384</v>
+      </c>
+      <c r="E234" s="43" t="s">
+        <v>1385</v>
+      </c>
+      <c r="F234" s="73"/>
+      <c r="G234" s="43"/>
+      <c r="H234" s="31"/>
+    </row>
+    <row r="235" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B235" s="43" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C235" s="43" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D235" s="43" t="s">
+        <v>1384</v>
+      </c>
+      <c r="E235" s="43" t="s">
+        <v>1385</v>
+      </c>
+      <c r="F235" s="73"/>
+      <c r="G235" s="43"/>
+      <c r="H235" s="31"/>
+    </row>
+    <row r="236" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B236" s="43" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C236" s="43" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D236" s="43" t="s">
+        <v>1384</v>
+      </c>
+      <c r="E236" s="43" t="s">
+        <v>1385</v>
+      </c>
+      <c r="F236" s="73"/>
+      <c r="G236" s="43"/>
+      <c r="H236" s="31"/>
+    </row>
+    <row r="237" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B237" s="43" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C237" s="43" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D237" s="43" t="s">
+        <v>1390</v>
+      </c>
+      <c r="E237" s="43" t="s">
+        <v>1385</v>
+      </c>
+      <c r="F237" s="73" t="s">
+        <v>1364</v>
+      </c>
+      <c r="G237" s="43" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H237" s="31">
+        <v>0.35</v>
+      </c>
+      <c r="J237" s="29" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B238" s="29" t="s">
+        <v>286</v>
+      </c>
+      <c r="C238" s="43" t="s">
+        <v>1393</v>
+      </c>
+      <c r="D238" s="42" t="s">
+        <v>1394</v>
+      </c>
+      <c r="E238" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="F238" s="30"/>
+      <c r="G238" s="30"/>
+      <c r="H238" s="31" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11" ht="36" customHeight="1">
+      <c r="A239" s="29"/>
+      <c r="B239" s="29" t="s">
+        <v>458</v>
+      </c>
+      <c r="C239" s="29" t="s">
+        <v>1395</v>
+      </c>
+      <c r="D239" s="29" t="s">
+        <v>460</v>
+      </c>
+      <c r="E239" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="F239" s="30"/>
+      <c r="G239" s="30"/>
+      <c r="H239" s="30"/>
+      <c r="I239" s="30"/>
+      <c r="J239" s="30"/>
+      <c r="K239" s="30"/>
+    </row>
+    <row r="240" spans="1:11" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B240" s="43" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C240" s="43" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D240" s="42" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E240" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="F240" s="30"/>
+      <c r="G240" s="30"/>
+      <c r="H240" s="31"/>
+    </row>
+    <row r="241" spans="2:8" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B241" s="43" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C241" s="43" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D241" s="42" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E241" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="F241" s="30"/>
+      <c r="G241" s="30"/>
+      <c r="H241" s="31"/>
+    </row>
+    <row r="242" spans="2:8" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B242" s="43" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C242" s="43" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D242" s="42" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E242" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="F242" s="30"/>
+      <c r="G242" s="30"/>
+      <c r="H242" s="31"/>
+    </row>
+    <row r="243" spans="2:8" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B243" s="43" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C243" s="43" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D243" s="42" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E243" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="F243" s="30"/>
+      <c r="G243" s="30"/>
+      <c r="H243" s="31"/>
+    </row>
+    <row r="244" spans="2:8" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B244" s="43" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C244" s="43" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D244" s="42" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E244" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="F244" s="30"/>
+      <c r="G244" s="30"/>
+      <c r="H244" s="31"/>
+    </row>
+    <row r="245" spans="2:8" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B245" s="43" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C245" s="43" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D245" s="42" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E245" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="F245" s="30"/>
+      <c r="G245" s="30"/>
+      <c r="H245" s="31"/>
+    </row>
+    <row r="246" spans="2:8" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B246" s="43" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C246" s="43" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D246" s="42" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E246" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="F246" s="30"/>
+      <c r="G246" s="30"/>
+      <c r="H246" s="31"/>
+    </row>
+    <row r="247" spans="2:8" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B247" s="43" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C247" s="43" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D247" s="42" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E247" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="F247" s="30"/>
+      <c r="G247" s="30"/>
+      <c r="H247" s="31"/>
+    </row>
+    <row r="248" spans="2:8" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B248" s="43" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C248" s="43" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D248" s="42" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E248" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="F248" s="30"/>
+      <c r="G248" s="30"/>
+      <c r="H248" s="31"/>
+    </row>
+    <row r="249" spans="2:8" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="B249" s="43" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C249" s="43" t="s">
+        <v>1408</v>
+      </c>
+      <c r="D249" s="42" t="s">
+        <v>1406</v>
+      </c>
+      <c r="E249" s="43" t="s">
+        <v>85</v>
+      </c>
+      <c r="F249" s="30"/>
+      <c r="G249" s="30"/>
+      <c r="H249" s="31"/>
+    </row>
+    <row r="250" spans="2:8" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="C250" s="43"/>
+      <c r="D250" s="42"/>
+      <c r="F250" s="30"/>
+      <c r="G250" s="30"/>
+      <c r="H250" s="31"/>
+    </row>
+    <row r="251" spans="2:8" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="C251" s="43"/>
+      <c r="D251" s="42"/>
+      <c r="F251" s="30"/>
+      <c r="G251" s="30"/>
+      <c r="H251" s="31"/>
+    </row>
+    <row r="252" spans="2:8" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="C252" s="43"/>
+      <c r="D252" s="42"/>
+      <c r="F252" s="30"/>
+      <c r="G252" s="30"/>
+      <c r="H252" s="31"/>
+    </row>
+    <row r="253" spans="2:8" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="C253" s="43"/>
+      <c r="D253" s="42"/>
+      <c r="F253" s="30"/>
+      <c r="G253" s="30"/>
+      <c r="H253" s="31"/>
+    </row>
+    <row r="254" spans="2:8" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="C254" s="43"/>
+      <c r="D254" s="42"/>
+      <c r="F254" s="30"/>
+      <c r="G254" s="30"/>
+      <c r="H254" s="31"/>
+    </row>
+    <row r="255" spans="2:8" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="C255" s="43"/>
+      <c r="D255" s="42"/>
+      <c r="F255" s="30"/>
+      <c r="G255" s="30"/>
+      <c r="H255" s="31"/>
+    </row>
+    <row r="256" spans="2:8" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="C256" s="43"/>
+      <c r="D256" s="42"/>
+      <c r="F256" s="30"/>
+      <c r="G256" s="30"/>
+      <c r="H256" s="31"/>
+    </row>
+    <row r="257" spans="3:8" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="C257" s="43"/>
+      <c r="D257" s="42"/>
+      <c r="F257" s="30"/>
+      <c r="G257" s="30"/>
+      <c r="H257" s="31"/>
+    </row>
+    <row r="258" spans="3:8" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="C258" s="43"/>
+      <c r="D258" s="42"/>
+      <c r="F258" s="30"/>
+      <c r="G258" s="30"/>
+      <c r="H258" s="31"/>
+    </row>
+    <row r="259" spans="3:8" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="C259" s="43"/>
+      <c r="D259" s="42"/>
+      <c r="F259" s="30"/>
+      <c r="G259" s="30"/>
+      <c r="H259" s="31"/>
+    </row>
+    <row r="260" spans="3:8" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="C260" s="43"/>
+      <c r="D260" s="42"/>
+      <c r="F260" s="30"/>
+      <c r="G260" s="30"/>
+      <c r="H260" s="31"/>
+    </row>
+    <row r="261" spans="3:8" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="C261" s="43"/>
+      <c r="D261" s="42"/>
+      <c r="F261" s="30"/>
+      <c r="G261" s="30"/>
+      <c r="H261" s="31"/>
+    </row>
+    <row r="262" spans="3:8" s="29" customFormat="1" ht="36" customHeight="1">
+      <c r="C262" s="43"/>
+      <c r="D262" s="42"/>
+      <c r="F262" s="30"/>
+      <c r="G262" s="30"/>
+      <c r="H262" s="31"/>
     </row>
   </sheetData>
   <phoneticPr fontId="20" type="noConversion"/>
@@ -12693,7 +14388,7 @@
         <v>777</v>
       </c>
       <c r="I2" s="52" t="s">
-        <v>1211</v>
+        <v>1200</v>
       </c>
       <c r="J2" s="22">
         <v>4</v>
@@ -12702,7 +14397,7 @@
         <v>4.2</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>1257</v>
+        <v>1245</v>
       </c>
       <c r="M2" s="18"/>
       <c r="N2" s="9" t="s">
@@ -12721,13 +14416,13 @@
         <v>794</v>
       </c>
       <c r="S2" s="64" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="T2" s="39" t="s">
-        <v>1209</v>
+        <v>1198</v>
       </c>
       <c r="U2" s="53" t="s">
-        <v>1210</v>
+        <v>1199</v>
       </c>
       <c r="V2" s="8"/>
       <c r="W2" s="8"/>
@@ -12760,10 +14455,10 @@
         <v>781</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I3" s="42" t="s">
-        <v>1248</v>
+        <v>1236</v>
       </c>
       <c r="J3" s="22">
         <v>3.9</v>
@@ -12772,11 +14467,11 @@
         <v>4</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>1279</v>
+        <v>1267</v>
       </c>
       <c r="M3" s="18"/>
       <c r="N3" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O3" s="8" t="s">
         <v>780</v>
@@ -12792,10 +14487,10 @@
         <v>783</v>
       </c>
       <c r="T3" s="29" t="s">
-        <v>1246</v>
+        <v>1234</v>
       </c>
       <c r="U3" s="42" t="s">
-        <v>1247</v>
+        <v>1235</v>
       </c>
       <c r="V3" s="8"/>
       <c r="W3" s="8"/>
@@ -12828,10 +14523,10 @@
         <v>991</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I4" s="64" t="s">
-        <v>1216</v>
+        <v>1205</v>
       </c>
       <c r="J4" s="22">
         <v>3.9</v>
@@ -12841,10 +14536,10 @@
       </c>
       <c r="L4" s="10"/>
       <c r="M4" s="18" t="s">
-        <v>1278</v>
+        <v>1266</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O4" s="8" t="s">
         <v>785</v>
@@ -12862,10 +14557,10 @@
         <v>1160</v>
       </c>
       <c r="T4" s="39" t="s">
-        <v>1206</v>
+        <v>1195</v>
       </c>
       <c r="U4" s="39" t="s">
-        <v>1207</v>
+        <v>1196</v>
       </c>
       <c r="V4" s="8"/>
       <c r="W4" s="8"/>
@@ -12898,10 +14593,10 @@
         <v>991</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I5" s="64" t="s">
-        <v>1214</v>
+        <v>1203</v>
       </c>
       <c r="J5" s="22">
         <v>4</v>
@@ -12911,10 +14606,10 @@
       </c>
       <c r="L5" s="10"/>
       <c r="M5" s="18" t="s">
-        <v>1278</v>
+        <v>1266</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O5" s="8" t="s">
         <v>787</v>
@@ -12932,10 +14627,10 @@
         <v>1160</v>
       </c>
       <c r="T5" s="53" t="s">
-        <v>1212</v>
+        <v>1201</v>
       </c>
       <c r="U5" s="39" t="s">
-        <v>1213</v>
+        <v>1202</v>
       </c>
       <c r="V5" s="8"/>
       <c r="W5" s="8"/>
@@ -12968,10 +14663,10 @@
         <v>991</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I6" s="68" t="s">
-        <v>1215</v>
+        <v>1204</v>
       </c>
       <c r="J6" s="22">
         <v>4.2</v>
@@ -12981,10 +14676,10 @@
       </c>
       <c r="L6" s="10"/>
       <c r="M6" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O6" s="8" t="s">
         <v>792</v>
@@ -13002,10 +14697,10 @@
         <v>1160</v>
       </c>
       <c r="T6" s="53" t="s">
-        <v>1205</v>
+        <v>1194</v>
       </c>
       <c r="U6" s="53" t="s">
-        <v>1208</v>
+        <v>1197</v>
       </c>
       <c r="V6" s="8"/>
       <c r="W6" s="8"/>
@@ -13048,7 +14743,7 @@
         <v>4</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M7" s="18"/>
       <c r="N7" s="9" t="s">
@@ -13067,7 +14762,7 @@
         <v>794</v>
       </c>
       <c r="S7" s="64" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="T7" s="8"/>
       <c r="U7" s="8"/>
@@ -13112,7 +14807,7 @@
         <v>4.2</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M8" s="18"/>
       <c r="N8" s="9" t="s">
@@ -13131,7 +14826,7 @@
         <v>794</v>
       </c>
       <c r="S8" s="64" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="T8" s="8"/>
       <c r="U8" s="8"/>
@@ -13176,7 +14871,7 @@
         <v>4</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M9" s="18"/>
       <c r="N9" s="9" t="s">
@@ -13195,7 +14890,7 @@
         <v>794</v>
       </c>
       <c r="S9" s="64" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="T9" s="8"/>
       <c r="U9" s="8"/>
@@ -13230,7 +14925,7 @@
         <v>798</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="22">
@@ -13241,10 +14936,10 @@
       </c>
       <c r="L10" s="10"/>
       <c r="M10" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O10" s="8" t="s">
         <v>785</v>
@@ -13302,7 +14997,7 @@
         <v>3.6</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M11" s="18"/>
       <c r="N11" s="9" t="s">
@@ -13321,7 +15016,7 @@
         <v>794</v>
       </c>
       <c r="S11" s="64" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="T11" s="8"/>
       <c r="U11" s="8"/>
@@ -13347,7 +15042,7 @@
         <v>吟麗 SUMMER</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>1265</v>
+        <v>1253</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>788</v>
@@ -13367,13 +15062,13 @@
       </c>
       <c r="L12" s="10"/>
       <c r="M12" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N12" s="8" t="s">
         <v>802</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>1265</v>
+        <v>1253</v>
       </c>
       <c r="P12" s="10">
         <v>1180</v>
@@ -13428,7 +15123,7 @@
         <v>3.8</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M13" s="18"/>
       <c r="N13" s="9" t="s">
@@ -13447,7 +15142,7 @@
         <v>794</v>
       </c>
       <c r="S13" s="64" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="T13" s="8"/>
       <c r="U13" s="8"/>
@@ -13492,7 +15187,7 @@
         <v>3.9</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M14" s="18"/>
       <c r="N14" s="9" t="s">
@@ -13511,7 +15206,7 @@
         <v>794</v>
       </c>
       <c r="S14" s="64" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="T14" s="8"/>
       <c r="U14" s="8"/>
@@ -13557,7 +15252,7 @@
       </c>
       <c r="L15" s="10"/>
       <c r="M15" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N15" s="9" t="s">
         <v>806</v>
@@ -13620,7 +15315,7 @@
         <v>4</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M16" s="18"/>
       <c r="N16" s="9" t="s">
@@ -13639,7 +15334,7 @@
         <v>794</v>
       </c>
       <c r="S16" s="64" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="T16" s="8"/>
       <c r="U16" s="8"/>
@@ -13684,7 +15379,7 @@
         <v>4</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M17" s="18"/>
       <c r="N17" s="9" t="s">
@@ -13703,7 +15398,7 @@
         <v>794</v>
       </c>
       <c r="S17" s="64" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="T17" s="8"/>
       <c r="U17" s="8"/>
@@ -13748,7 +15443,7 @@
         <v>3.9</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M18" s="18"/>
       <c r="N18" s="9" t="s">
@@ -13767,7 +15462,7 @@
         <v>794</v>
       </c>
       <c r="S18" s="64" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="T18" s="8"/>
       <c r="U18" s="8"/>
@@ -13812,7 +15507,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M19" s="18"/>
       <c r="N19" s="9" t="s">
@@ -13831,7 +15526,7 @@
         <v>794</v>
       </c>
       <c r="S19" s="64" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="T19" s="8"/>
       <c r="U19" s="8"/>
@@ -13876,7 +15571,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M20" s="18"/>
       <c r="N20" s="9" t="s">
@@ -13895,7 +15590,7 @@
         <v>794</v>
       </c>
       <c r="S20" s="64" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="T20" s="8"/>
       <c r="U20" s="8"/>
@@ -13940,7 +15635,7 @@
         <v>4</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M21" s="18"/>
       <c r="N21" s="9" t="s">
@@ -13959,7 +15654,7 @@
         <v>794</v>
       </c>
       <c r="S21" s="64" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="T21" s="8"/>
       <c r="U21" s="8"/>
@@ -14004,7 +15699,7 @@
         <v>4</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M22" s="18"/>
       <c r="N22" s="9" t="s">
@@ -14023,7 +15718,7 @@
         <v>794</v>
       </c>
       <c r="S22" s="64" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="T22" s="8"/>
       <c r="U22" s="8"/>
@@ -14071,7 +15766,7 @@
       </c>
       <c r="L23" s="10"/>
       <c r="M23" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N23" s="8" t="s">
         <v>802</v>
@@ -14087,7 +15782,7 @@
         <v>790</v>
       </c>
       <c r="S23" s="39" t="s">
-        <v>1295</v>
+        <v>1283</v>
       </c>
       <c r="U23" s="8"/>
       <c r="V23" s="8"/>
@@ -14126,7 +15821,7 @@
         <v>801</v>
       </c>
       <c r="I24" s="67" t="s">
-        <v>1182</v>
+        <v>1345</v>
       </c>
       <c r="J24" s="22">
         <v>3.5</v>
@@ -14136,10 +15831,10 @@
       </c>
       <c r="L24" s="10"/>
       <c r="M24" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N24" s="8" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O24" s="8" t="s">
         <v>780</v>
@@ -14157,10 +15852,10 @@
         <v>819</v>
       </c>
       <c r="T24" s="65" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="U24" s="67" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="V24" s="8"/>
       <c r="W24" s="8"/>
@@ -14195,10 +15890,10 @@
         <v>789</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I25" s="67" t="s">
-        <v>1181</v>
+        <v>1344</v>
       </c>
       <c r="J25" s="22">
         <v>3.5</v>
@@ -14208,10 +15903,10 @@
       </c>
       <c r="L25" s="10"/>
       <c r="M25" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N25" s="8" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O25" s="8" t="s">
         <v>818</v>
@@ -14229,10 +15924,10 @@
         <v>822</v>
       </c>
       <c r="T25" s="65" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="U25" s="67" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="V25" s="8"/>
       <c r="W25" s="8"/>
@@ -14270,7 +15965,7 @@
         <v>801</v>
       </c>
       <c r="I26" s="52" t="s">
-        <v>1197</v>
+        <v>1346</v>
       </c>
       <c r="J26" s="22">
         <v>3.5</v>
@@ -14280,10 +15975,10 @@
       </c>
       <c r="L26" s="10"/>
       <c r="M26" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N26" s="8" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O26" s="8" t="s">
         <v>821</v>
@@ -14301,10 +15996,10 @@
         <v>824</v>
       </c>
       <c r="T26" s="53" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="U26" s="39" t="s">
-        <v>1204</v>
+        <v>1193</v>
       </c>
       <c r="V26" s="8"/>
       <c r="W26" s="8"/>
@@ -14339,10 +16034,10 @@
         <v>789</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I27" s="43" t="s">
-        <v>1198</v>
+        <v>1347</v>
       </c>
       <c r="J27" s="22">
         <v>3.8</v>
@@ -14352,10 +16047,10 @@
       </c>
       <c r="L27" s="10"/>
       <c r="M27" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N27" s="8" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O27" s="8" t="s">
         <v>780</v>
@@ -14373,10 +16068,10 @@
         <v>826</v>
       </c>
       <c r="T27" s="53" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="U27" s="49" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="V27" s="8"/>
       <c r="W27" s="8"/>
@@ -14411,10 +16106,10 @@
         <v>789</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I28" s="67" t="s">
-        <v>1199</v>
+        <v>1348</v>
       </c>
       <c r="J28" s="22">
         <v>4</v>
@@ -14424,10 +16119,10 @@
       </c>
       <c r="L28" s="10"/>
       <c r="M28" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N28" s="8" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O28" s="8" t="s">
         <v>792</v>
@@ -14445,10 +16140,10 @@
         <v>828</v>
       </c>
       <c r="T28" s="53" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="U28" s="39" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="V28" s="8"/>
       <c r="W28" s="8"/>
@@ -14486,7 +16181,7 @@
         <v>801</v>
       </c>
       <c r="I29" s="42" t="s">
-        <v>1203</v>
+        <v>1349</v>
       </c>
       <c r="J29" s="22">
         <v>3.8</v>
@@ -14496,10 +16191,10 @@
       </c>
       <c r="L29" s="10"/>
       <c r="M29" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N29" s="8" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O29" s="8" t="s">
         <v>818</v>
@@ -14517,10 +16212,10 @@
         <v>830</v>
       </c>
       <c r="T29" s="43" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="U29" s="39" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="V29" s="8"/>
       <c r="W29" s="8"/>
@@ -14555,10 +16250,10 @@
         <v>789</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I30" s="52" t="s">
-        <v>1201</v>
+        <v>1350</v>
       </c>
       <c r="J30" s="22">
         <v>3.8</v>
@@ -14568,10 +16263,10 @@
       </c>
       <c r="L30" s="10"/>
       <c r="M30" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N30" s="8" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O30" s="8" t="s">
         <v>792</v>
@@ -14589,10 +16284,10 @@
         <v>832</v>
       </c>
       <c r="T30" s="53" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="U30" s="39" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="V30" s="8"/>
       <c r="W30" s="8"/>
@@ -14630,7 +16325,7 @@
         <v>801</v>
       </c>
       <c r="I31" s="52" t="s">
-        <v>1200</v>
+        <v>1351</v>
       </c>
       <c r="J31" s="22">
         <v>3.9</v>
@@ -14640,10 +16335,10 @@
       </c>
       <c r="L31" s="10"/>
       <c r="M31" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N31" s="8" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O31" s="8" t="s">
         <v>821</v>
@@ -14661,10 +16356,10 @@
         <v>834</v>
       </c>
       <c r="T31" s="53" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="U31" s="39" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="V31" s="8"/>
       <c r="W31" s="8"/>
@@ -14702,17 +16397,17 @@
         <v>801</v>
       </c>
       <c r="I32" s="54" t="s">
-        <v>1202</v>
+        <v>1352</v>
       </c>
       <c r="J32" s="22">
-        <v>4.4000000000000004</v>
+        <v>4.5</v>
       </c>
       <c r="K32" s="22">
         <v>4.5</v>
       </c>
       <c r="L32" s="10"/>
       <c r="M32" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N32" s="8" t="s">
         <v>836</v>
@@ -14733,10 +16428,10 @@
         <v>837</v>
       </c>
       <c r="T32" s="66" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="U32" s="39" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="V32" s="8"/>
       <c r="W32" s="8"/>
@@ -14774,7 +16469,7 @@
         <v>801</v>
       </c>
       <c r="I33" s="42" t="s">
-        <v>1219</v>
+        <v>1353</v>
       </c>
       <c r="J33" s="22">
         <v>3.9</v>
@@ -14784,10 +16479,10 @@
       </c>
       <c r="L33" s="10"/>
       <c r="M33" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N33" s="8" t="s">
-        <v>1240</v>
+        <v>1228</v>
       </c>
       <c r="O33" s="8" t="s">
         <v>787</v>
@@ -14805,10 +16500,10 @@
         <v>839</v>
       </c>
       <c r="T33" s="42" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="U33" s="39" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="V33" s="8"/>
       <c r="W33" s="8"/>
@@ -14853,7 +16548,7 @@
         <v>4</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M34" s="18"/>
       <c r="N34" s="9" t="s">
@@ -14872,7 +16567,7 @@
         <v>794</v>
       </c>
       <c r="S34" s="64" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="T34" s="8"/>
       <c r="U34" s="8"/>
@@ -14917,7 +16612,7 @@
         <v>3.8</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M35" s="18"/>
       <c r="N35" s="9" t="s">
@@ -14936,7 +16631,7 @@
         <v>794</v>
       </c>
       <c r="S35" s="64" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="T35" s="8"/>
       <c r="U35" s="8"/>
@@ -14981,7 +16676,7 @@
         <v>4</v>
       </c>
       <c r="L36" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M36" s="18"/>
       <c r="N36" s="9" t="s">
@@ -15000,7 +16695,7 @@
         <v>794</v>
       </c>
       <c r="S36" s="15" t="s">
-        <v>1220</v>
+        <v>1208</v>
       </c>
       <c r="T36" s="8"/>
       <c r="U36" s="8"/>
@@ -15045,7 +16740,7 @@
         <v>3.5</v>
       </c>
       <c r="L37" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M37" s="18"/>
       <c r="N37" s="26" t="s">
@@ -15064,7 +16759,7 @@
         <v>794</v>
       </c>
       <c r="S37" s="15" t="s">
-        <v>1220</v>
+        <v>1208</v>
       </c>
       <c r="T37" s="8"/>
       <c r="U37" s="8"/>
@@ -15109,7 +16804,7 @@
         <v>3.4</v>
       </c>
       <c r="L38" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M38" s="18"/>
       <c r="N38" s="26" t="s">
@@ -15128,7 +16823,7 @@
         <v>794</v>
       </c>
       <c r="S38" s="15" t="s">
-        <v>1220</v>
+        <v>1208</v>
       </c>
       <c r="T38" s="8"/>
       <c r="U38" s="8"/>
@@ -15173,7 +16868,7 @@
         <v>4</v>
       </c>
       <c r="L39" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M39" s="18"/>
       <c r="N39" s="26" t="s">
@@ -15192,7 +16887,7 @@
         <v>794</v>
       </c>
       <c r="S39" s="15" t="s">
-        <v>1220</v>
+        <v>1208</v>
       </c>
       <c r="T39" s="8"/>
       <c r="U39" s="8"/>
@@ -15237,7 +16932,7 @@
         <v>3.5</v>
       </c>
       <c r="L40" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M40" s="18"/>
       <c r="N40" s="26" t="s">
@@ -15256,7 +16951,7 @@
         <v>794</v>
       </c>
       <c r="S40" s="15" t="s">
-        <v>1220</v>
+        <v>1208</v>
       </c>
       <c r="T40" s="8"/>
       <c r="U40" s="8"/>
@@ -15301,7 +16996,7 @@
         <v>4</v>
       </c>
       <c r="L41" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M41" s="18"/>
       <c r="N41" s="26" t="s">
@@ -15320,7 +17015,7 @@
         <v>794</v>
       </c>
       <c r="S41" s="15" t="s">
-        <v>1220</v>
+        <v>1208</v>
       </c>
       <c r="T41" s="8"/>
       <c r="U41" s="8"/>
@@ -15365,7 +17060,7 @@
         <v>3.6</v>
       </c>
       <c r="L42" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M42" s="18"/>
       <c r="N42" s="26" t="s">
@@ -15384,7 +17079,7 @@
         <v>794</v>
       </c>
       <c r="S42" s="15" t="s">
-        <v>1220</v>
+        <v>1208</v>
       </c>
       <c r="T42" s="8"/>
       <c r="U42" s="8"/>
@@ -15429,7 +17124,7 @@
         <v>3.7</v>
       </c>
       <c r="L43" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M43" s="18"/>
       <c r="N43" s="26" t="s">
@@ -15448,7 +17143,7 @@
         <v>794</v>
       </c>
       <c r="S43" s="15" t="s">
-        <v>1220</v>
+        <v>1208</v>
       </c>
       <c r="T43" s="8"/>
       <c r="U43" s="8"/>
@@ -15493,7 +17188,7 @@
         <v>3.5</v>
       </c>
       <c r="L44" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M44" s="18"/>
       <c r="N44" s="26" t="s">
@@ -15512,7 +17207,7 @@
         <v>794</v>
       </c>
       <c r="S44" s="15" t="s">
-        <v>1220</v>
+        <v>1208</v>
       </c>
       <c r="T44" s="8"/>
       <c r="U44" s="8"/>
@@ -15557,7 +17252,7 @@
         <v>3.6</v>
       </c>
       <c r="L45" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M45" s="18"/>
       <c r="N45" s="26" t="s">
@@ -15576,7 +17271,7 @@
         <v>794</v>
       </c>
       <c r="S45" s="15" t="s">
-        <v>1220</v>
+        <v>1208</v>
       </c>
       <c r="T45" s="8"/>
       <c r="U45" s="8"/>
@@ -15621,7 +17316,7 @@
         <v>3.6</v>
       </c>
       <c r="L46" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M46" s="18"/>
       <c r="N46" s="26" t="s">
@@ -15640,7 +17335,7 @@
         <v>794</v>
       </c>
       <c r="S46" s="15" t="s">
-        <v>1220</v>
+        <v>1208</v>
       </c>
       <c r="T46" s="8"/>
       <c r="U46" s="8"/>
@@ -15685,7 +17380,7 @@
         <v>3.5</v>
       </c>
       <c r="L47" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M47" s="18"/>
       <c r="N47" s="26" t="s">
@@ -15704,7 +17399,7 @@
         <v>794</v>
       </c>
       <c r="S47" s="15" t="s">
-        <v>1220</v>
+        <v>1208</v>
       </c>
       <c r="T47" s="8"/>
       <c r="U47" s="8"/>
@@ -15749,7 +17444,7 @@
         <v>3.5</v>
       </c>
       <c r="L48" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M48" s="18"/>
       <c r="N48" s="26" t="s">
@@ -15768,7 +17463,7 @@
         <v>794</v>
       </c>
       <c r="S48" s="15" t="s">
-        <v>1220</v>
+        <v>1208</v>
       </c>
       <c r="T48" s="8"/>
       <c r="U48" s="8"/>
@@ -15806,7 +17501,7 @@
         <v>859</v>
       </c>
       <c r="I49" s="64" t="s">
-        <v>1304</v>
+        <v>1292</v>
       </c>
       <c r="J49" s="22">
         <v>4</v>
@@ -15816,10 +17511,10 @@
       </c>
       <c r="L49" s="10"/>
       <c r="M49" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N49" s="13" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="O49" s="8" t="s">
         <v>858</v>
@@ -15834,13 +17529,13 @@
         <v>790</v>
       </c>
       <c r="S49" s="15" t="s">
-        <v>1263</v>
+        <v>1251</v>
       </c>
       <c r="T49" s="39" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="U49" s="39" t="s">
-        <v>1303</v>
+        <v>1291</v>
       </c>
       <c r="V49" s="8"/>
       <c r="W49" s="8"/>
@@ -15884,7 +17579,7 @@
       </c>
       <c r="L50" s="10"/>
       <c r="M50" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N50" s="15" t="s">
         <v>1142</v>
@@ -15945,7 +17640,7 @@
         <v>3.6</v>
       </c>
       <c r="L51" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M51" s="18"/>
       <c r="N51" s="8" t="s">
@@ -15991,7 +17686,7 @@
         <v>789</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I52" s="9"/>
       <c r="J52" s="22">
@@ -16001,11 +17696,11 @@
         <v>4</v>
       </c>
       <c r="L52" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M52" s="18"/>
       <c r="N52" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O52" s="8" t="s">
         <v>780</v>
@@ -16030,7 +17725,7 @@
     </row>
     <row r="53" spans="1:26" ht="57.95" customHeight="1">
       <c r="A53" s="8" t="s">
-        <v>1354</v>
+        <v>1339</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>685</v>
@@ -16053,7 +17748,7 @@
         <v>789</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I53" s="9"/>
       <c r="J53" s="22">
@@ -16064,10 +17759,10 @@
       </c>
       <c r="L53" s="10"/>
       <c r="M53" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O53" s="8" t="s">
         <v>780</v>
@@ -16115,7 +17810,7 @@
         <v>789</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I54" s="9"/>
       <c r="J54" s="22">
@@ -16126,10 +17821,10 @@
       </c>
       <c r="L54" s="10"/>
       <c r="M54" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N54" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O54" s="8" t="s">
         <v>792</v>
@@ -16177,10 +17872,10 @@
         <v>789</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I55" s="47" t="s">
-        <v>1297</v>
+        <v>1285</v>
       </c>
       <c r="J55" s="22">
         <v>3.8</v>
@@ -16189,11 +17884,11 @@
         <v>3.8</v>
       </c>
       <c r="L55" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M55" s="18"/>
       <c r="N55" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O55" s="8" t="s">
         <v>792</v>
@@ -16209,10 +17904,10 @@
       </c>
       <c r="S55" s="9"/>
       <c r="T55" s="39" t="s">
-        <v>1298</v>
+        <v>1286</v>
       </c>
       <c r="U55" s="39" t="s">
-        <v>1296</v>
+        <v>1284</v>
       </c>
       <c r="V55" s="8"/>
       <c r="W55" s="8"/>
@@ -16236,7 +17931,7 @@
         <v>SEA 純米</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>775</v>
@@ -16245,7 +17940,7 @@
         <v>776</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I56" s="9"/>
       <c r="J56" s="22">
@@ -16255,11 +17950,11 @@
         <v>4</v>
       </c>
       <c r="L56" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M56" s="18"/>
       <c r="N56" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O56" s="8" t="s">
         <v>870</v>
@@ -16309,7 +18004,7 @@
         <v>781</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="22">
@@ -16319,11 +18014,11 @@
         <v>4</v>
       </c>
       <c r="L57" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M57" s="18"/>
       <c r="N57" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O57" s="8" t="s">
         <v>870</v>
@@ -16367,7 +18062,7 @@
         <v>781</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I58" s="9"/>
       <c r="J58" s="22">
@@ -16377,11 +18072,11 @@
         <v>4</v>
       </c>
       <c r="L58" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M58" s="18"/>
       <c r="N58" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O58" s="8" t="s">
         <v>861</v>
@@ -16435,7 +18130,7 @@
         <v>4</v>
       </c>
       <c r="L59" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M59" s="18"/>
       <c r="N59" s="9" t="s">
@@ -16454,7 +18149,7 @@
         <v>794</v>
       </c>
       <c r="S59" s="64" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="T59" s="8"/>
       <c r="U59" s="8"/>
@@ -16499,7 +18194,7 @@
         <v>4</v>
       </c>
       <c r="L60" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M60" s="18"/>
       <c r="N60" s="9" t="s">
@@ -16518,7 +18213,7 @@
         <v>794</v>
       </c>
       <c r="S60" s="64" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="T60" s="8"/>
       <c r="U60" s="8"/>
@@ -16563,7 +18258,7 @@
         <v>4</v>
       </c>
       <c r="L61" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M61" s="18"/>
       <c r="N61" s="9" t="s">
@@ -16582,7 +18277,7 @@
         <v>794</v>
       </c>
       <c r="S61" s="64" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="T61" s="8"/>
       <c r="U61" s="8"/>
@@ -16627,7 +18322,7 @@
         <v>3.8</v>
       </c>
       <c r="L62" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M62" s="18"/>
       <c r="N62" s="9" t="s">
@@ -16646,7 +18341,7 @@
         <v>794</v>
       </c>
       <c r="S62" s="64" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="T62" s="8"/>
       <c r="U62" s="8"/>
@@ -16691,7 +18386,7 @@
         <v>3.5</v>
       </c>
       <c r="L63" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M63" s="18"/>
       <c r="N63" s="9" t="s">
@@ -16710,7 +18405,7 @@
         <v>794</v>
       </c>
       <c r="S63" s="64" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="T63" s="8"/>
       <c r="U63" s="8"/>
@@ -16745,7 +18440,7 @@
         <v>789</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I64" s="9"/>
       <c r="J64" s="22">
@@ -16755,11 +18450,11 @@
         <v>3.8</v>
       </c>
       <c r="L64" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M64" s="18"/>
       <c r="N64" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O64" s="11" t="s">
         <v>1161</v>
@@ -16807,7 +18502,7 @@
         <v>789</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I65" s="9"/>
       <c r="J65" s="22">
@@ -16817,11 +18512,11 @@
         <v>3.8</v>
       </c>
       <c r="L65" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M65" s="18"/>
       <c r="N65" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O65" s="11" t="s">
         <v>880</v>
@@ -16869,7 +18564,7 @@
         <v>789</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I66" s="9"/>
       <c r="J66" s="22">
@@ -16880,10 +18575,10 @@
       </c>
       <c r="L66" s="10"/>
       <c r="M66" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N66" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O66" s="11" t="s">
         <v>880</v>
@@ -16942,13 +18637,13 @@
       </c>
       <c r="L67" s="10"/>
       <c r="M67" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N67" s="17" t="s">
-        <v>1243</v>
+        <v>1231</v>
       </c>
       <c r="O67" s="11" t="s">
-        <v>1245</v>
+        <v>1233</v>
       </c>
       <c r="P67" s="10"/>
       <c r="Q67" s="8" t="s">
@@ -16991,7 +18686,7 @@
         <v>789</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I68" s="9"/>
       <c r="J68" s="22">
@@ -17002,10 +18697,10 @@
       </c>
       <c r="L68" s="10"/>
       <c r="M68" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N68" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O68" s="11" t="s">
         <v>880</v>
@@ -17053,7 +18748,7 @@
         <v>789</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="22">
@@ -17063,11 +18758,11 @@
         <v>3.8</v>
       </c>
       <c r="L69" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M69" s="18"/>
       <c r="N69" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O69" s="11" t="s">
         <v>880</v>
@@ -17115,7 +18810,7 @@
         <v>789</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I70" s="9"/>
       <c r="J70" s="22">
@@ -17125,11 +18820,11 @@
         <v>3.6</v>
       </c>
       <c r="L70" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M70" s="18"/>
       <c r="N70" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O70" s="11" t="s">
         <v>880</v>
@@ -17187,11 +18882,11 @@
         <v>4</v>
       </c>
       <c r="L71" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M71" s="18"/>
       <c r="N71" s="51" t="s">
-        <v>1274</v>
+        <v>1262</v>
       </c>
       <c r="O71" s="8" t="s">
         <v>888</v>
@@ -17247,11 +18942,11 @@
         <v>4.2</v>
       </c>
       <c r="L72" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M72" s="18"/>
       <c r="N72" s="51" t="s">
-        <v>1274</v>
+        <v>1262</v>
       </c>
       <c r="O72" s="8" t="s">
         <v>888</v>
@@ -17308,10 +19003,10 @@
       </c>
       <c r="L73" s="10"/>
       <c r="M73" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N73" s="51" t="s">
-        <v>1274</v>
+        <v>1262</v>
       </c>
       <c r="O73" s="8" t="s">
         <v>888</v>
@@ -17370,10 +19065,10 @@
       </c>
       <c r="L74" s="10"/>
       <c r="M74" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N74" s="51" t="s">
-        <v>1274</v>
+        <v>1262</v>
       </c>
       <c r="O74" s="8" t="s">
         <v>888</v>
@@ -17431,11 +19126,11 @@
         <v>4</v>
       </c>
       <c r="L75" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M75" s="18"/>
       <c r="N75" s="51" t="s">
-        <v>1274</v>
+        <v>1262</v>
       </c>
       <c r="O75" s="8" t="s">
         <v>888</v>
@@ -17487,11 +19182,11 @@
         <v>4</v>
       </c>
       <c r="L76" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M76" s="18"/>
       <c r="N76" s="51" t="s">
-        <v>1274</v>
+        <v>1262</v>
       </c>
       <c r="O76" s="8" t="s">
         <v>888</v>
@@ -17543,11 +19238,11 @@
         <v>4.3</v>
       </c>
       <c r="L77" s="10" t="s">
-        <v>1259</v>
+        <v>1247</v>
       </c>
       <c r="M77" s="18"/>
       <c r="N77" s="51" t="s">
-        <v>1274</v>
+        <v>1262</v>
       </c>
       <c r="O77" s="8" t="s">
         <v>888</v>
@@ -17556,7 +19251,7 @@
       <c r="Q77" s="8"/>
       <c r="R77" s="8"/>
       <c r="S77" s="15" t="s">
-        <v>1294</v>
+        <v>1282</v>
       </c>
       <c r="T77" s="8"/>
       <c r="U77" s="8"/>
@@ -17591,7 +19286,7 @@
         <v>789</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I78" s="9"/>
       <c r="J78" s="22">
@@ -17601,11 +19296,11 @@
         <v>3.6</v>
       </c>
       <c r="L78" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M78" s="18"/>
       <c r="N78" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O78" s="8" t="s">
         <v>896</v>
@@ -17630,7 +19325,7 @@
     </row>
     <row r="79" spans="1:26" ht="57.95" customHeight="1">
       <c r="A79" s="8" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>271</v>
@@ -17656,7 +19351,7 @@
         <v>1157</v>
       </c>
       <c r="I79" s="47" t="s">
-        <v>1316</v>
+        <v>1303</v>
       </c>
       <c r="J79" s="22">
         <v>3.6</v>
@@ -17665,11 +19360,11 @@
         <v>3.6</v>
       </c>
       <c r="L79" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M79" s="18"/>
       <c r="N79" s="8" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="O79" s="8" t="s">
         <v>896</v>
@@ -17685,10 +19380,10 @@
         <v>1162</v>
       </c>
       <c r="T79" s="39" t="s">
-        <v>1314</v>
+        <v>1301</v>
       </c>
       <c r="U79" s="49" t="s">
-        <v>1315</v>
+        <v>1302</v>
       </c>
       <c r="V79" s="8"/>
       <c r="W79" s="8"/>
@@ -17724,7 +19419,7 @@
         <v>1157</v>
       </c>
       <c r="I80" s="15" t="s">
-        <v>1308</v>
+        <v>1295</v>
       </c>
       <c r="J80" s="22">
         <v>3.5</v>
@@ -17733,11 +19428,11 @@
         <v>3.5</v>
       </c>
       <c r="L80" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M80" s="18"/>
       <c r="N80" s="27" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="O80" s="8" t="s">
         <v>896</v>
@@ -17753,10 +19448,10 @@
         <v>1162</v>
       </c>
       <c r="T80" s="49" t="s">
-        <v>1307</v>
+        <v>1294</v>
       </c>
       <c r="U80" s="49" t="s">
-        <v>1312</v>
+        <v>1299</v>
       </c>
       <c r="V80" s="8"/>
       <c r="W80" s="8"/>
@@ -17792,7 +19487,7 @@
         <v>1157</v>
       </c>
       <c r="I81" s="15" t="s">
-        <v>1313</v>
+        <v>1300</v>
       </c>
       <c r="J81" s="22">
         <v>3.6</v>
@@ -17801,11 +19496,11 @@
         <v>3.7</v>
       </c>
       <c r="L81" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M81" s="18"/>
       <c r="N81" s="27" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="O81" s="8" t="s">
         <v>896</v>
@@ -17821,10 +19516,10 @@
         <v>1162</v>
       </c>
       <c r="T81" s="49" t="s">
-        <v>1309</v>
+        <v>1296</v>
       </c>
       <c r="U81" s="49" t="s">
-        <v>1310</v>
+        <v>1297</v>
       </c>
       <c r="V81" s="8"/>
       <c r="W81" s="8"/>
@@ -17859,8 +19554,8 @@
       <c r="H82" s="52" t="s">
         <v>1157</v>
       </c>
-      <c r="I82" s="72" t="s">
-        <v>1317</v>
+      <c r="I82" s="71" t="s">
+        <v>1304</v>
       </c>
       <c r="J82" s="22">
         <v>3.8</v>
@@ -17869,11 +19564,11 @@
         <v>4</v>
       </c>
       <c r="L82" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M82" s="18"/>
       <c r="N82" s="27" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="O82" s="8" t="s">
         <v>896</v>
@@ -17889,10 +19584,10 @@
         <v>1162</v>
       </c>
       <c r="T82" s="49" t="s">
-        <v>1311</v>
+        <v>1298</v>
       </c>
       <c r="U82" s="49" t="s">
-        <v>1322</v>
+        <v>1308</v>
       </c>
       <c r="V82" s="8"/>
       <c r="W82" s="8"/>
@@ -17916,7 +19611,7 @@
         <v>玄達 〜GENTATSU〜 純米吟釀</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>1221</v>
+        <v>1209</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>775</v>
@@ -17925,7 +19620,7 @@
         <v>991</v>
       </c>
       <c r="H83" s="15" t="s">
-        <v>1223</v>
+        <v>1211</v>
       </c>
       <c r="I83" s="9"/>
       <c r="J83" s="22">
@@ -17935,14 +19630,14 @@
         <v>4</v>
       </c>
       <c r="L83" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M83" s="18"/>
       <c r="N83" s="8" t="s">
-        <v>1222</v>
+        <v>1210</v>
       </c>
       <c r="O83" s="8" t="s">
-        <v>1221</v>
+        <v>1209</v>
       </c>
       <c r="P83" s="10"/>
       <c r="Q83" s="8"/>
@@ -17984,7 +19679,7 @@
         <v>1157</v>
       </c>
       <c r="I84" s="52" t="s">
-        <v>1320</v>
+        <v>1306</v>
       </c>
       <c r="J84" s="22">
         <v>3.7</v>
@@ -17993,14 +19688,14 @@
         <v>3.8</v>
       </c>
       <c r="L84" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M84" s="18"/>
       <c r="N84" s="27" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="O84" s="11" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P84" s="10"/>
       <c r="Q84" s="8" t="s">
@@ -18013,10 +19708,10 @@
         <v>1162</v>
       </c>
       <c r="T84" s="51" t="s">
-        <v>1319</v>
+        <v>1305</v>
       </c>
       <c r="U84" s="51" t="s">
-        <v>1324</v>
+        <v>1310</v>
       </c>
       <c r="V84" s="8"/>
       <c r="W84" s="8"/>
@@ -18051,8 +19746,8 @@
       <c r="H85" s="53" t="s">
         <v>1157</v>
       </c>
-      <c r="I85" s="73" t="s">
-        <v>1328</v>
+      <c r="I85" s="72" t="s">
+        <v>1314</v>
       </c>
       <c r="J85" s="22">
         <v>3.6</v>
@@ -18061,14 +19756,14 @@
         <v>3.6</v>
       </c>
       <c r="L85" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M85" s="18"/>
       <c r="N85" s="27" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="O85" s="11" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P85" s="10"/>
       <c r="Q85" s="8" t="s">
@@ -18081,10 +19776,10 @@
         <v>1162</v>
       </c>
       <c r="T85" s="46" t="s">
-        <v>1321</v>
+        <v>1307</v>
       </c>
       <c r="U85" s="46" t="s">
-        <v>1323</v>
+        <v>1309</v>
       </c>
       <c r="V85" s="8"/>
       <c r="W85" s="8"/>
@@ -18120,7 +19815,7 @@
         <v>1157</v>
       </c>
       <c r="I86" s="64" t="s">
-        <v>1327</v>
+        <v>1313</v>
       </c>
       <c r="J86" s="22">
         <v>3.3</v>
@@ -18129,14 +19824,14 @@
         <v>3.3</v>
       </c>
       <c r="L86" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M86" s="18"/>
       <c r="N86" s="27" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="O86" s="11" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P86" s="10"/>
       <c r="Q86" s="8" t="s">
@@ -18149,10 +19844,10 @@
         <v>1162</v>
       </c>
       <c r="T86" s="51" t="s">
-        <v>1325</v>
+        <v>1311</v>
       </c>
       <c r="U86" s="53" t="s">
-        <v>1326</v>
+        <v>1312</v>
       </c>
       <c r="V86" s="8"/>
       <c r="W86" s="8"/>
@@ -18187,8 +19882,8 @@
       <c r="H87" s="53" t="s">
         <v>1157</v>
       </c>
-      <c r="I87" s="73" t="s">
-        <v>1331</v>
+      <c r="I87" s="72" t="s">
+        <v>1317</v>
       </c>
       <c r="J87" s="22">
         <v>3.6</v>
@@ -18197,14 +19892,14 @@
         <v>3.7</v>
       </c>
       <c r="L87" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M87" s="18"/>
       <c r="N87" s="27" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="O87" s="11" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P87" s="10"/>
       <c r="Q87" s="8" t="s">
@@ -18217,10 +19912,10 @@
         <v>1162</v>
       </c>
       <c r="T87" s="51" t="s">
-        <v>1329</v>
+        <v>1315</v>
       </c>
       <c r="U87" s="51" t="s">
-        <v>1330</v>
+        <v>1316</v>
       </c>
       <c r="V87" s="8"/>
       <c r="W87" s="8"/>
@@ -18256,7 +19951,7 @@
         <v>1157</v>
       </c>
       <c r="I88" s="47" t="s">
-        <v>1334</v>
+        <v>1320</v>
       </c>
       <c r="J88" s="22">
         <v>3.6</v>
@@ -18266,13 +19961,13 @@
       </c>
       <c r="L88" s="10"/>
       <c r="M88" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N88" s="27" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="O88" s="11" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P88" s="10"/>
       <c r="Q88" s="8" t="s">
@@ -18285,10 +19980,10 @@
         <v>1162</v>
       </c>
       <c r="T88" s="65" t="s">
-        <v>1333</v>
+        <v>1319</v>
       </c>
       <c r="U88" s="39" t="s">
-        <v>1332</v>
+        <v>1318</v>
       </c>
       <c r="V88" s="8"/>
       <c r="W88" s="8"/>
@@ -18324,7 +20019,7 @@
         <v>1157</v>
       </c>
       <c r="I89" s="52" t="s">
-        <v>1338</v>
+        <v>1324</v>
       </c>
       <c r="J89" s="22">
         <v>4</v>
@@ -18334,13 +20029,13 @@
       </c>
       <c r="L89" s="10"/>
       <c r="M89" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N89" s="27" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="O89" s="11" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P89" s="10">
         <v>3850</v>
@@ -18355,10 +20050,10 @@
         <v>1165</v>
       </c>
       <c r="T89" s="49" t="s">
-        <v>1335</v>
+        <v>1321</v>
       </c>
       <c r="U89" s="39" t="s">
-        <v>1336</v>
+        <v>1322</v>
       </c>
       <c r="V89" s="8"/>
       <c r="W89" s="8"/>
@@ -18391,10 +20086,10 @@
         <v>789</v>
       </c>
       <c r="H90" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I90" s="52" t="s">
-        <v>1337</v>
+        <v>1323</v>
       </c>
       <c r="J90" s="22">
         <v>3.9</v>
@@ -18404,10 +20099,10 @@
       </c>
       <c r="L90" s="10"/>
       <c r="M90" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N90" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O90" s="8" t="s">
         <v>908</v>
@@ -18460,7 +20155,7 @@
         <v>1157</v>
       </c>
       <c r="I91" s="47" t="s">
-        <v>1340</v>
+        <v>1326</v>
       </c>
       <c r="J91" s="22">
         <v>3.6</v>
@@ -18469,14 +20164,14 @@
         <v>3.6</v>
       </c>
       <c r="L91" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M91" s="18"/>
       <c r="N91" s="27" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="O91" s="11" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P91" s="10"/>
       <c r="Q91" s="8" t="s">
@@ -18489,10 +20184,10 @@
         <v>1162</v>
       </c>
       <c r="T91" s="39" t="s">
-        <v>1339</v>
+        <v>1325</v>
       </c>
       <c r="U91" s="39" t="s">
-        <v>1342</v>
+        <v>1328</v>
       </c>
       <c r="V91" s="8"/>
       <c r="W91" s="8"/>
@@ -18528,7 +20223,7 @@
         <v>1157</v>
       </c>
       <c r="I92" s="64" t="s">
-        <v>1344</v>
+        <v>1330</v>
       </c>
       <c r="J92" s="22">
         <v>3.7</v>
@@ -18537,14 +20232,14 @@
         <v>3.7</v>
       </c>
       <c r="L92" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M92" s="18"/>
       <c r="N92" s="27" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="O92" s="11" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P92" s="10"/>
       <c r="Q92" s="8" t="s">
@@ -18557,10 +20252,10 @@
         <v>1162</v>
       </c>
       <c r="T92" s="49" t="s">
-        <v>1341</v>
+        <v>1327</v>
       </c>
       <c r="U92" s="49" t="s">
-        <v>1343</v>
+        <v>1329</v>
       </c>
       <c r="V92" s="8"/>
       <c r="W92" s="8"/>
@@ -18596,7 +20291,7 @@
         <v>1157</v>
       </c>
       <c r="I93" s="47" t="s">
-        <v>1348</v>
+        <v>1334</v>
       </c>
       <c r="J93" s="22">
         <v>3.8</v>
@@ -18605,14 +20300,14 @@
         <v>3.8</v>
       </c>
       <c r="L93" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M93" s="18"/>
       <c r="N93" s="27" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="O93" s="11" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P93" s="10"/>
       <c r="Q93" s="8" t="s">
@@ -18625,10 +20320,10 @@
         <v>1162</v>
       </c>
       <c r="T93" s="49" t="s">
-        <v>1347</v>
+        <v>1333</v>
       </c>
       <c r="U93" s="49" t="s">
-        <v>1345</v>
+        <v>1331</v>
       </c>
       <c r="V93" s="8"/>
       <c r="W93" s="8"/>
@@ -18664,7 +20359,7 @@
         <v>1157</v>
       </c>
       <c r="I94" s="15" t="s">
-        <v>1350</v>
+        <v>1336</v>
       </c>
       <c r="J94" s="22">
         <v>3.7</v>
@@ -18673,14 +20368,14 @@
         <v>3.8</v>
       </c>
       <c r="L94" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M94" s="18"/>
       <c r="N94" s="27" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="O94" s="11" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P94" s="10"/>
       <c r="Q94" s="8" t="s">
@@ -18693,10 +20388,10 @@
         <v>1162</v>
       </c>
       <c r="T94" s="49" t="s">
-        <v>1346</v>
+        <v>1332</v>
       </c>
       <c r="U94" s="39" t="s">
-        <v>1349</v>
+        <v>1335</v>
       </c>
       <c r="V94" s="8"/>
       <c r="W94" s="8"/>
@@ -18720,7 +20415,7 @@
         <v>純米 愛山807</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>1225</v>
+        <v>1213</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>788</v>
@@ -18740,13 +20435,13 @@
       </c>
       <c r="L95" s="10"/>
       <c r="M95" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N95" s="8" t="s">
-        <v>1240</v>
+        <v>1228</v>
       </c>
       <c r="O95" s="11" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="P95" s="10">
         <v>1800</v>
@@ -18801,14 +20496,14 @@
         <v>4.5</v>
       </c>
       <c r="L96" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M96" s="18"/>
       <c r="N96" s="27" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="O96" s="11" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P96" s="10">
         <v>600</v>
@@ -18844,7 +20539,7 @@
         <v>蔵元限定 ひとごこち</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>1226</v>
+        <v>1214</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>788</v>
@@ -18853,7 +20548,7 @@
         <v>991</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I97" s="9"/>
       <c r="J97" s="22">
@@ -18864,13 +20559,13 @@
       </c>
       <c r="L97" s="10"/>
       <c r="M97" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O97" s="8" t="s">
-        <v>1226</v>
+        <v>1214</v>
       </c>
       <c r="P97" s="10">
         <v>5200</v>
@@ -18915,7 +20610,7 @@
         <v>789</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I98" s="9"/>
       <c r="J98" s="22">
@@ -18925,14 +20620,14 @@
         <v>4.5</v>
       </c>
       <c r="L98" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M98" s="18"/>
       <c r="N98" s="8" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="O98" s="11" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P98" s="10">
         <v>1200</v>
@@ -18988,13 +20683,13 @@
       </c>
       <c r="L99" s="10"/>
       <c r="M99" s="18" t="s">
-        <v>1278</v>
+        <v>1266</v>
       </c>
       <c r="N99" s="17" t="s">
-        <v>1243</v>
+        <v>1231</v>
       </c>
       <c r="O99" s="11" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P99" s="10">
         <v>11800</v>
@@ -19039,7 +20734,7 @@
         <v>789</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I100" s="9"/>
       <c r="J100" s="22">
@@ -19050,13 +20745,13 @@
       </c>
       <c r="L100" s="10"/>
       <c r="M100" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N100" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O100" s="11" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="P100" s="10">
         <v>5500</v>
@@ -19092,10 +20787,10 @@
         <v>越淡麗 無濾過直汲 荒走</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>1266</v>
+        <v>1254</v>
       </c>
       <c r="G101" s="8" t="s">
         <v>789</v>
@@ -19112,13 +20807,13 @@
       </c>
       <c r="L101" s="10"/>
       <c r="M101" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N101" s="8" t="s">
-        <v>1240</v>
+        <v>1228</v>
       </c>
       <c r="O101" s="11" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="P101" s="10">
         <v>1680</v>
@@ -19154,7 +20849,7 @@
         <v>山廢特別純米 愛山70 直汲み 無濾過生原酒</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>788</v>
@@ -19174,13 +20869,13 @@
       </c>
       <c r="L102" s="10"/>
       <c r="M102" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N102" s="8" t="s">
-        <v>1240</v>
+        <v>1228</v>
       </c>
       <c r="O102" s="11" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="P102" s="10">
         <v>1780</v>
@@ -19216,7 +20911,7 @@
         <v>中汲 純米大吟釀 生酒</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>788</v>
@@ -19236,13 +20931,13 @@
       </c>
       <c r="L103" s="10"/>
       <c r="M103" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N103" s="8" t="s">
-        <v>1240</v>
+        <v>1228</v>
       </c>
       <c r="O103" s="8" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="P103" s="10">
         <v>1680</v>
@@ -19264,7 +20959,7 @@
     </row>
     <row r="104" spans="1:26" ht="57.95" customHeight="1">
       <c r="A104" s="8" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="B104" s="8" t="s">
         <v>372</v>
@@ -19298,7 +20993,7 @@
       </c>
       <c r="L104" s="10"/>
       <c r="M104" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N104" s="8" t="s">
         <v>1149</v>
@@ -19354,7 +21049,7 @@
       </c>
       <c r="L105" s="10"/>
       <c r="M105" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N105" s="8" t="s">
         <v>1148</v>
@@ -19410,7 +21105,7 @@
       </c>
       <c r="L106" s="10"/>
       <c r="M106" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N106" s="39" t="s">
         <v>1143</v>
@@ -19466,10 +21161,10 @@
       </c>
       <c r="L107" s="10"/>
       <c r="M107" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N107" s="8" t="s">
-        <v>1239</v>
+        <v>1227</v>
       </c>
       <c r="O107" s="8" t="s">
         <v>1146</v>
@@ -19528,7 +21223,7 @@
       </c>
       <c r="L108" s="10"/>
       <c r="M108" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N108" s="39" t="s">
         <v>1144</v>
@@ -19590,10 +21285,10 @@
       </c>
       <c r="L109" s="10"/>
       <c r="M109" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N109" s="8" t="s">
-        <v>1239</v>
+        <v>1227</v>
       </c>
       <c r="O109" s="8" t="s">
         <v>1146</v>
@@ -19632,7 +21327,7 @@
         <v>2023 大吟釀28 Nobilmente</v>
       </c>
       <c r="E110" s="11" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>775</v>
@@ -19651,14 +21346,14 @@
         <v>4</v>
       </c>
       <c r="L110" s="10" t="s">
-        <v>1249</v>
+        <v>1237</v>
       </c>
       <c r="M110" s="18"/>
       <c r="N110" s="39" t="s">
         <v>1145</v>
       </c>
       <c r="O110" s="11" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="P110" s="10">
         <v>900</v>
@@ -19714,10 +21409,10 @@
       </c>
       <c r="L111" s="10"/>
       <c r="M111" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N111" s="8" t="s">
-        <v>1240</v>
+        <v>1228</v>
       </c>
       <c r="O111" s="11" t="s">
         <v>1158</v>
@@ -19756,7 +21451,7 @@
         <v>純米吟釀 初榨</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>788</v>
@@ -19776,13 +21471,13 @@
       </c>
       <c r="L112" s="10"/>
       <c r="M112" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N112" s="8" t="s">
-        <v>1240</v>
+        <v>1228</v>
       </c>
       <c r="O112" s="8" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="P112" s="10">
         <v>2980</v>
@@ -19818,7 +21513,7 @@
         <v>純米大吟釀 for taiwan</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>788</v>
@@ -19838,13 +21533,13 @@
       </c>
       <c r="L113" s="10"/>
       <c r="M113" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N113" s="8" t="s">
-        <v>1239</v>
+        <v>1227</v>
       </c>
       <c r="O113" s="8" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="P113" s="10">
         <v>1220</v>
@@ -19889,7 +21584,7 @@
         <v>789</v>
       </c>
       <c r="H114" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I114" s="9"/>
       <c r="J114" s="22">
@@ -19899,11 +21594,11 @@
         <v>4</v>
       </c>
       <c r="L114" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M114" s="18"/>
       <c r="N114" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O114" s="8" t="s">
         <v>1161</v>
@@ -19947,7 +21642,7 @@
         <v>1147</v>
       </c>
       <c r="I115" s="15" t="s">
-        <v>1171</v>
+        <v>1343</v>
       </c>
       <c r="J115" s="22">
         <v>3.8</v>
@@ -19957,10 +21652,10 @@
       </c>
       <c r="L115" s="10"/>
       <c r="M115" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N115" s="8" t="s">
-        <v>1240</v>
+        <v>1228</v>
       </c>
       <c r="O115" s="8" t="s">
         <v>1158</v>
@@ -20012,10 +21707,10 @@
         <v>789</v>
       </c>
       <c r="H116" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I116" s="15" t="s">
-        <v>1172</v>
+        <v>1342</v>
       </c>
       <c r="J116" s="22">
         <v>3.8</v>
@@ -20025,10 +21720,10 @@
       </c>
       <c r="L116" s="10"/>
       <c r="M116" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N116" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O116" s="8" t="s">
         <v>1166</v>
@@ -20083,13 +21778,13 @@
       </c>
       <c r="L117" s="10"/>
       <c r="M117" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N117" s="46" t="s">
-        <v>1241</v>
+        <v>1229</v>
       </c>
       <c r="O117" s="11" t="s">
-        <v>1268</v>
+        <v>1256</v>
       </c>
       <c r="P117" s="10">
         <v>1250</v>
@@ -20143,13 +21838,13 @@
       </c>
       <c r="L118" s="10"/>
       <c r="M118" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N118" s="46" t="s">
         <v>1153</v>
       </c>
       <c r="O118" s="11" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="P118" s="10">
         <v>1550</v>
@@ -20205,10 +21900,10 @@
       </c>
       <c r="L119" s="10"/>
       <c r="M119" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N119" s="27" t="s">
-        <v>1222</v>
+        <v>1210</v>
       </c>
       <c r="O119" s="11" t="s">
         <v>1146</v>
@@ -20265,13 +21960,13 @@
       </c>
       <c r="L120" s="10"/>
       <c r="M120" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N120" s="46" t="s">
-        <v>1241</v>
+        <v>1229</v>
       </c>
       <c r="O120" s="11" t="s">
-        <v>1268</v>
+        <v>1256</v>
       </c>
       <c r="P120" s="10">
         <v>1500</v>
@@ -20327,10 +22022,10 @@
       </c>
       <c r="L121" s="10"/>
       <c r="M121" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N121" s="39" t="s">
-        <v>1254</v>
+        <v>1242</v>
       </c>
       <c r="O121" s="11" t="s">
         <v>1146</v>
@@ -20369,7 +22064,7 @@
         <v>純米吟釀 搾立</v>
       </c>
       <c r="E122" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>788</v>
@@ -20378,7 +22073,7 @@
         <v>789</v>
       </c>
       <c r="H122" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I122" s="9"/>
       <c r="J122" s="22">
@@ -20389,13 +22084,13 @@
       </c>
       <c r="L122" s="10"/>
       <c r="M122" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N122" s="39" t="s">
-        <v>1256</v>
+        <v>1244</v>
       </c>
       <c r="O122" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="P122" s="10">
         <v>1700</v>
@@ -20431,7 +22126,7 @@
         <v>夏虫 純米吟釀</v>
       </c>
       <c r="E123" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="F123" s="8" t="s">
         <v>775</v>
@@ -20440,7 +22135,7 @@
         <v>776</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I123" s="9"/>
       <c r="J123" s="22">
@@ -20450,14 +22145,14 @@
         <v>3.7</v>
       </c>
       <c r="L123" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M123" s="18"/>
       <c r="N123" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O123" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="P123" s="10"/>
       <c r="Q123" s="8" t="s">
@@ -20491,7 +22186,7 @@
         <v>黑鐵 純米吟釀</v>
       </c>
       <c r="E124" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="F124" s="8" t="s">
         <v>775</v>
@@ -20500,7 +22195,7 @@
         <v>776</v>
       </c>
       <c r="H124" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I124" s="9"/>
       <c r="J124" s="22">
@@ -20510,14 +22205,14 @@
         <v>3.5</v>
       </c>
       <c r="L124" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M124" s="18"/>
       <c r="N124" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O124" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="P124" s="10"/>
       <c r="Q124" s="8" t="s">
@@ -20551,7 +22246,7 @@
         <v>真紅 純米吟釀</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="F125" s="8" t="s">
         <v>775</v>
@@ -20560,7 +22255,7 @@
         <v>776</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I125" s="9"/>
       <c r="J125" s="22">
@@ -20570,14 +22265,14 @@
         <v>3.5</v>
       </c>
       <c r="L125" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M125" s="18"/>
       <c r="N125" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O125" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="P125" s="10"/>
       <c r="Q125" s="8" t="s">
@@ -20611,7 +22306,7 @@
         <v>櫻鼠 純米吟釀</v>
       </c>
       <c r="E126" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="F126" s="8" t="s">
         <v>775</v>
@@ -20620,7 +22315,7 @@
         <v>776</v>
       </c>
       <c r="H126" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I126" s="9"/>
       <c r="J126" s="22">
@@ -20630,14 +22325,14 @@
         <v>3.7</v>
       </c>
       <c r="L126" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M126" s="18"/>
       <c r="N126" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O126" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="P126" s="10"/>
       <c r="Q126" s="8" t="s">
@@ -20671,7 +22366,7 @@
         <v>極走 純米大吟釀生酒</v>
       </c>
       <c r="E127" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="F127" s="8" t="s">
         <v>788</v>
@@ -20680,7 +22375,7 @@
         <v>789</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I127" s="9"/>
       <c r="J127" s="22">
@@ -20691,13 +22386,13 @@
       </c>
       <c r="L127" s="10"/>
       <c r="M127" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O127" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="P127" s="10">
         <v>1780</v>
@@ -20709,7 +22404,7 @@
         <v>790</v>
       </c>
       <c r="S127" s="9" t="s">
-        <v>1255</v>
+        <v>1243</v>
       </c>
       <c r="T127" s="8"/>
       <c r="U127" s="8"/>
@@ -20755,7 +22450,7 @@
       </c>
       <c r="L128" s="10"/>
       <c r="M128" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N128" s="39" t="s">
         <v>1143</v>
@@ -20791,7 +22486,7 @@
         <v>Abe black</v>
       </c>
       <c r="E129" s="8" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="F129" s="8" t="s">
         <v>788</v>
@@ -20800,7 +22495,7 @@
         <v>789</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I129" s="9"/>
       <c r="J129" s="22">
@@ -20811,13 +22506,13 @@
       </c>
       <c r="L129" s="10"/>
       <c r="M129" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O129" s="8" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="P129" s="10">
         <v>3160</v>
@@ -20864,7 +22559,7 @@
         <v>789</v>
       </c>
       <c r="H130" s="52" t="s">
-        <v>1229</v>
+        <v>1217</v>
       </c>
       <c r="I130" s="9"/>
       <c r="J130" s="22">
@@ -20875,7 +22570,7 @@
       </c>
       <c r="L130" s="10"/>
       <c r="M130" s="18" t="s">
-        <v>1278</v>
+        <v>1266</v>
       </c>
       <c r="N130" s="49" t="s">
         <v>1150</v>
@@ -20926,7 +22621,7 @@
         <v>776</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I131" s="9"/>
       <c r="J131" s="22">
@@ -20936,11 +22631,11 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="L131" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M131" s="18"/>
       <c r="N131" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O131" s="8" t="s">
         <v>950</v>
@@ -20955,7 +22650,7 @@
         <v>794</v>
       </c>
       <c r="S131" s="52" t="s">
-        <v>1276</v>
+        <v>1264</v>
       </c>
       <c r="T131" s="8"/>
       <c r="U131" s="8"/>
@@ -20990,7 +22685,7 @@
         <v>776</v>
       </c>
       <c r="H132" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I132" s="9"/>
       <c r="J132" s="22">
@@ -21000,11 +22695,11 @@
         <v>3.8</v>
       </c>
       <c r="L132" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M132" s="18"/>
       <c r="N132" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O132" s="8" t="s">
         <v>950</v>
@@ -21019,7 +22714,7 @@
         <v>794</v>
       </c>
       <c r="S132" s="52" t="s">
-        <v>1276</v>
+        <v>1264</v>
       </c>
       <c r="T132" s="8"/>
       <c r="U132" s="8"/>
@@ -21054,7 +22749,7 @@
         <v>776</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="22">
@@ -21064,11 +22759,11 @@
         <v>3.8</v>
       </c>
       <c r="L133" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M133" s="18"/>
       <c r="N133" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O133" s="8" t="s">
         <v>950</v>
@@ -21083,7 +22778,7 @@
         <v>794</v>
       </c>
       <c r="S133" s="52" t="s">
-        <v>1276</v>
+        <v>1264</v>
       </c>
       <c r="T133" s="8"/>
       <c r="U133" s="8"/>
@@ -21118,7 +22813,7 @@
         <v>776</v>
       </c>
       <c r="H134" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I134" s="9"/>
       <c r="J134" s="22">
@@ -21128,11 +22823,11 @@
         <v>3.8</v>
       </c>
       <c r="L134" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M134" s="18"/>
       <c r="N134" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O134" s="8" t="s">
         <v>950</v>
@@ -21147,7 +22842,7 @@
         <v>794</v>
       </c>
       <c r="S134" s="52" t="s">
-        <v>1276</v>
+        <v>1264</v>
       </c>
       <c r="T134" s="8"/>
       <c r="U134" s="8"/>
@@ -21182,7 +22877,7 @@
         <v>776</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="22">
@@ -21192,11 +22887,11 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="L135" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M135" s="18"/>
       <c r="N135" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O135" s="8" t="s">
         <v>950</v>
@@ -21211,7 +22906,7 @@
         <v>794</v>
       </c>
       <c r="S135" s="52" t="s">
-        <v>1276</v>
+        <v>1264</v>
       </c>
       <c r="T135" s="8"/>
       <c r="U135" s="8"/>
@@ -21237,7 +22932,7 @@
         <v>火焰</v>
       </c>
       <c r="E136" s="8" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="F136" s="8" t="s">
         <v>788</v>
@@ -21257,13 +22952,13 @@
       </c>
       <c r="L136" s="10"/>
       <c r="M136" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N136" s="8" t="s">
-        <v>1240</v>
+        <v>1228</v>
       </c>
       <c r="O136" s="8" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="P136" s="10">
         <v>1800</v>
@@ -21299,7 +22994,7 @@
         <v>原始乃胎動 純米大吟釀 無濾過生原酒</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="F137" s="8" t="s">
         <v>788</v>
@@ -21319,10 +23014,10 @@
       </c>
       <c r="L137" s="10"/>
       <c r="M137" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N137" s="8" t="s">
-        <v>1240</v>
+        <v>1228</v>
       </c>
       <c r="O137" s="11" t="s">
         <v>1146</v>
@@ -21361,7 +23056,7 @@
         <v>Reserves</v>
       </c>
       <c r="E138" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="F138" s="8" t="s">
         <v>788</v>
@@ -21381,13 +23076,13 @@
       </c>
       <c r="L138" s="10"/>
       <c r="M138" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N138" s="39" t="s">
-        <v>1293</v>
+        <v>1281</v>
       </c>
       <c r="O138" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="P138" s="10"/>
       <c r="Q138" s="8"/>
@@ -21417,7 +23112,7 @@
         <v>1569xEUREKA!</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="F139" s="8" t="s">
         <v>788</v>
@@ -21426,7 +23121,7 @@
         <v>798</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I139" s="9"/>
       <c r="J139" s="22">
@@ -21437,13 +23132,13 @@
       </c>
       <c r="L139" s="10"/>
       <c r="M139" s="18" t="s">
-        <v>1280</v>
+        <v>1268</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O139" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="P139" s="10">
         <v>6000</v>
@@ -21465,7 +23160,7 @@
     </row>
     <row r="140" spans="1:26" ht="57.95" customHeight="1">
       <c r="A140" s="8" t="s">
-        <v>1299</v>
+        <v>1287</v>
       </c>
       <c r="B140" s="8" t="s">
         <v>497</v>
@@ -21479,7 +23174,7 @@
         <v>Pink</v>
       </c>
       <c r="E140" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="F140" s="8" t="s">
         <v>788</v>
@@ -21488,7 +23183,7 @@
         <v>789</v>
       </c>
       <c r="H140" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I140" s="9"/>
       <c r="J140" s="22">
@@ -21499,13 +23194,13 @@
       </c>
       <c r="L140" s="10"/>
       <c r="M140" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N140" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O140" s="8" t="s">
-        <v>1232</v>
+        <v>1220</v>
       </c>
       <c r="P140" s="10">
         <v>3850</v>
@@ -21541,7 +23236,7 @@
         <v>2026 山形讚香 純米大吟釀</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>1232</v>
+        <v>1220</v>
       </c>
       <c r="F141" s="8" t="s">
         <v>788</v>
@@ -21550,7 +23245,7 @@
         <v>991</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="22">
@@ -21561,13 +23256,13 @@
       </c>
       <c r="L141" s="10"/>
       <c r="M141" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O141" s="11" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="P141" s="10">
         <v>3980</v>
@@ -21603,7 +23298,7 @@
         <v>純米大吟釀 超辛口</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>1233</v>
+        <v>1221</v>
       </c>
       <c r="F142" s="8" t="s">
         <v>775</v>
@@ -21612,7 +23307,7 @@
         <v>789</v>
       </c>
       <c r="H142" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I142" s="9"/>
       <c r="J142" s="22">
@@ -21622,11 +23317,11 @@
         <v>4</v>
       </c>
       <c r="L142" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M142" s="18"/>
       <c r="N142" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O142" s="11" t="s">
         <v>1161</v>
@@ -21665,7 +23360,7 @@
         <v>出羽燦燦33</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>1234</v>
+        <v>1222</v>
       </c>
       <c r="F143" s="8" t="s">
         <v>788</v>
@@ -21685,13 +23380,13 @@
       </c>
       <c r="L143" s="10"/>
       <c r="M143" s="18" t="s">
-        <v>1278</v>
+        <v>1266</v>
       </c>
       <c r="N143" s="8" t="s">
-        <v>1240</v>
+        <v>1228</v>
       </c>
       <c r="O143" s="11" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="P143" s="10">
         <v>3880</v>
@@ -21727,7 +23422,7 @@
         <v>100週年 1&amp;2號 酵母混合</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="F144" s="8" t="s">
         <v>788</v>
@@ -21736,7 +23431,7 @@
         <v>789</v>
       </c>
       <c r="H144" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I144" s="9"/>
       <c r="J144" s="22">
@@ -21747,13 +23442,13 @@
       </c>
       <c r="L144" s="10"/>
       <c r="M144" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N144" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O144" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="P144" s="10">
         <v>6600</v>
@@ -21765,7 +23460,7 @@
         <v>790</v>
       </c>
       <c r="S144" s="15" t="s">
-        <v>1250</v>
+        <v>1238</v>
       </c>
       <c r="T144" s="8"/>
       <c r="U144" s="8"/>
@@ -21791,7 +23486,7 @@
         <v>純米大吟釀35 北雫(きたしずく)</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="F145" s="8" t="s">
         <v>788</v>
@@ -21800,7 +23495,7 @@
         <v>798</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I145" s="9"/>
       <c r="J145" s="22">
@@ -21811,19 +23506,19 @@
       </c>
       <c r="L145" s="10"/>
       <c r="M145" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O145" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="P145" s="10"/>
       <c r="Q145" s="8"/>
       <c r="R145" s="8"/>
       <c r="S145" s="15" t="s">
-        <v>1292</v>
+        <v>1280</v>
       </c>
       <c r="T145" s="8"/>
       <c r="U145" s="8"/>
@@ -21849,7 +23544,7 @@
         <v>漆黑 KURO 純米吟釀</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="F146" s="8" t="s">
         <v>788</v>
@@ -21869,13 +23564,13 @@
       </c>
       <c r="L146" s="10"/>
       <c r="M146" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N146" s="8" t="s">
-        <v>1240</v>
+        <v>1228</v>
       </c>
       <c r="O146" s="8" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="P146" s="10">
         <v>1680</v>
@@ -21911,7 +23606,7 @@
         <v>二割三分</v>
       </c>
       <c r="E147" s="8" t="s">
-        <v>1253</v>
+        <v>1241</v>
       </c>
       <c r="F147" s="8" t="s">
         <v>775</v>
@@ -21931,13 +23626,13 @@
       </c>
       <c r="L147" s="10"/>
       <c r="M147" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N147" s="15" t="s">
         <v>1143</v>
       </c>
       <c r="O147" s="8" t="s">
-        <v>1224</v>
+        <v>1212</v>
       </c>
       <c r="P147" s="10"/>
       <c r="Q147" s="8"/>
@@ -21976,7 +23671,7 @@
         <v>781</v>
       </c>
       <c r="H148" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I148" s="9"/>
       <c r="J148" s="22">
@@ -21986,11 +23681,11 @@
         <v>3.7</v>
       </c>
       <c r="L148" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M148" s="18"/>
       <c r="N148" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O148" s="11" t="s">
         <v>1158</v>
@@ -22023,7 +23718,7 @@
         <v>船中八策 純米超辛口</v>
       </c>
       <c r="E149" s="8" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="F149" s="8" t="s">
         <v>775</v>
@@ -22032,7 +23727,7 @@
         <v>781</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I149" s="9"/>
       <c r="J149" s="22">
@@ -22042,14 +23737,14 @@
         <v>3.6</v>
       </c>
       <c r="L149" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M149" s="18"/>
       <c r="N149" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O149" s="8" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P149" s="10"/>
       <c r="Q149" s="8"/>
@@ -22079,7 +23774,7 @@
         <v>船中八策　槽搾り 黑</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>775</v>
@@ -22088,7 +23783,7 @@
         <v>781</v>
       </c>
       <c r="H150" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I150" s="9"/>
       <c r="J150" s="22">
@@ -22098,14 +23793,14 @@
         <v>4</v>
       </c>
       <c r="L150" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M150" s="18"/>
       <c r="N150" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O150" s="8" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="P150" s="10"/>
       <c r="Q150" s="8"/>
@@ -22144,7 +23839,7 @@
         <v>991</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I151" s="9"/>
       <c r="J151" s="22">
@@ -22155,10 +23850,10 @@
       </c>
       <c r="L151" s="10"/>
       <c r="M151" s="18" t="s">
-        <v>1278</v>
+        <v>1266</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O151" s="8" t="s">
         <v>1158</v>
@@ -22208,7 +23903,7 @@
         <v>789</v>
       </c>
       <c r="H152" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I152" s="9"/>
       <c r="J152" s="22">
@@ -22219,10 +23914,10 @@
       </c>
       <c r="L152" s="10"/>
       <c r="M152" s="18" t="s">
-        <v>1278</v>
+        <v>1266</v>
       </c>
       <c r="N152" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O152" s="8" t="s">
         <v>1161</v>
@@ -22263,7 +23958,7 @@
         <v>秋田酒こまち 純米吟釀</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>1251</v>
+        <v>1239</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>788</v>
@@ -22272,7 +23967,7 @@
         <v>991</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I153" s="9"/>
       <c r="J153" s="22">
@@ -22283,13 +23978,13 @@
       </c>
       <c r="L153" s="10"/>
       <c r="M153" s="18" t="s">
-        <v>1278</v>
+        <v>1266</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O153" s="8" t="s">
-        <v>1251</v>
+        <v>1239</v>
       </c>
       <c r="P153" s="8">
         <v>6580</v>
@@ -22336,7 +24031,7 @@
         <v>798</v>
       </c>
       <c r="H154" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I154" s="9"/>
       <c r="J154" s="22">
@@ -22347,10 +24042,10 @@
       </c>
       <c r="L154" s="10"/>
       <c r="M154" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N154" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O154" s="11" t="s">
         <v>1158</v>
@@ -22359,7 +24054,7 @@
       <c r="Q154" s="8"/>
       <c r="R154" s="8"/>
       <c r="S154" s="15" t="s">
-        <v>1291</v>
+        <v>1279</v>
       </c>
       <c r="T154" s="8"/>
       <c r="U154" s="8"/>
@@ -22385,7 +24080,7 @@
         <v>黑鳳凰 純米吟釀</v>
       </c>
       <c r="E155" s="8" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="F155" s="8" t="s">
         <v>788</v>
@@ -22405,13 +24100,13 @@
       </c>
       <c r="L155" s="10"/>
       <c r="M155" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N155" s="8" t="s">
         <v>836</v>
       </c>
       <c r="O155" s="8" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P155" s="10">
         <v>1388</v>
@@ -22447,7 +24142,7 @@
         <v>純米大吟釀 雪女神 四割八分 火入れ</v>
       </c>
       <c r="E156" s="8" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>788</v>
@@ -22467,13 +24162,13 @@
       </c>
       <c r="L156" s="10"/>
       <c r="M156" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N156" s="39" t="s">
         <v>1143</v>
       </c>
       <c r="O156" s="8" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P156" s="10"/>
       <c r="Q156" s="8"/>
@@ -22523,7 +24218,7 @@
       </c>
       <c r="L157" s="10"/>
       <c r="M157" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N157" s="39" t="s">
         <v>1143</v>
@@ -22579,7 +24274,7 @@
       </c>
       <c r="L158" s="10"/>
       <c r="M158" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N158" s="39" t="s">
         <v>1143</v>
@@ -22618,13 +24313,13 @@
         <v>1158</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="G159" s="8" t="s">
         <v>776</v>
       </c>
       <c r="H159" s="9" t="s">
-        <v>1252</v>
+        <v>1240</v>
       </c>
       <c r="I159" s="9"/>
       <c r="J159" s="22">
@@ -22634,11 +24329,11 @@
         <v>4</v>
       </c>
       <c r="L159" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M159" s="18"/>
       <c r="N159" s="9" t="s">
-        <v>1252</v>
+        <v>1240</v>
       </c>
       <c r="O159" s="8" t="s">
         <v>1158</v>
@@ -22693,10 +24388,10 @@
       </c>
       <c r="L160" s="10"/>
       <c r="M160" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N160" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O160" s="8" t="s">
         <v>870</v>
@@ -22748,7 +24443,7 @@
         <v>789</v>
       </c>
       <c r="H161" s="15" t="s">
-        <v>1230</v>
+        <v>1218</v>
       </c>
       <c r="I161" s="9"/>
       <c r="J161" s="22">
@@ -22759,10 +24454,10 @@
       </c>
       <c r="L161" s="10"/>
       <c r="M161" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N161" s="8" t="s">
-        <v>1239</v>
+        <v>1227</v>
       </c>
       <c r="O161" s="8" t="s">
         <v>883</v>
@@ -22801,7 +24496,7 @@
         <v>2026 夏日獨角仙 KABUTOMUSHI 純米大吟釀</v>
       </c>
       <c r="E162" s="8" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="F162" s="8" t="s">
         <v>775</v>
@@ -22810,7 +24505,7 @@
         <v>781</v>
       </c>
       <c r="H162" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I162" s="9"/>
       <c r="J162" s="22">
@@ -22820,14 +24515,14 @@
         <v>3.6</v>
       </c>
       <c r="L162" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M162" s="18"/>
       <c r="N162" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O162" s="11" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="P162" s="10"/>
       <c r="Q162" s="8"/>
@@ -22857,7 +24552,7 @@
         <v>RETRO 零式 生酒</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="F163" s="8" t="s">
         <v>788</v>
@@ -22877,13 +24572,13 @@
       </c>
       <c r="L163" s="10"/>
       <c r="M163" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N163" s="8" t="s">
-        <v>1239</v>
+        <v>1227</v>
       </c>
       <c r="O163" s="11" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="P163" s="10">
         <v>1380</v>
@@ -22939,10 +24634,10 @@
       </c>
       <c r="L164" s="10"/>
       <c r="M164" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N164" s="8" t="s">
-        <v>1238</v>
+        <v>1226</v>
       </c>
       <c r="O164" s="11" t="s">
         <v>1161</v>
@@ -22981,7 +24676,7 @@
         <v>うまうまシリーズ 八甲田牛 吟醸原酒</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>788</v>
@@ -23001,13 +24696,13 @@
       </c>
       <c r="L165" s="10"/>
       <c r="M165" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N165" s="8" t="s">
         <v>1154</v>
       </c>
       <c r="O165" s="11" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="P165" s="10">
         <v>1880</v>
@@ -23043,7 +24738,7 @@
         <v>「溪」2024 ★</v>
       </c>
       <c r="E166" s="8" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="F166" s="8" t="s">
         <v>775</v>
@@ -23052,7 +24747,7 @@
         <v>776</v>
       </c>
       <c r="H166" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I166" s="9"/>
       <c r="J166" s="22">
@@ -23062,14 +24757,14 @@
         <v>3.6</v>
       </c>
       <c r="L166" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M166" s="18"/>
       <c r="N166" s="9" t="s">
-        <v>1237</v>
+        <v>1225</v>
       </c>
       <c r="O166" s="11" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="P166" s="10">
         <v>800</v>
@@ -23105,7 +24800,7 @@
         <v>超 王祿 2024★</v>
       </c>
       <c r="E167" s="8" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="F167" s="8" t="s">
         <v>775</v>
@@ -23114,7 +24809,7 @@
         <v>776</v>
       </c>
       <c r="H167" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I167" s="9"/>
       <c r="J167" s="22">
@@ -23124,14 +24819,14 @@
         <v>3.6</v>
       </c>
       <c r="L167" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M167" s="18"/>
       <c r="N167" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O167" s="11" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="P167" s="10">
         <v>800</v>
@@ -23167,7 +24862,7 @@
         <v>王祿「八〇」2023 ★★★</v>
       </c>
       <c r="E168" s="8" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="F168" s="8" t="s">
         <v>775</v>
@@ -23176,7 +24871,7 @@
         <v>776</v>
       </c>
       <c r="H168" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I168" s="9"/>
       <c r="J168" s="22">
@@ -23186,14 +24881,14 @@
         <v>3.7</v>
       </c>
       <c r="L168" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M168" s="18"/>
       <c r="N168" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O168" s="11" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="P168" s="10">
         <v>800</v>
@@ -23229,7 +24924,7 @@
         <v>純米生酒</v>
       </c>
       <c r="E169" s="8" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="F169" s="8" t="s">
         <v>775</v>
@@ -23238,7 +24933,7 @@
         <v>789</v>
       </c>
       <c r="H169" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I169" s="9"/>
       <c r="J169" s="22">
@@ -23248,14 +24943,14 @@
         <v>3.7</v>
       </c>
       <c r="L169" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M169" s="18"/>
       <c r="N169" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O169" s="11" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="P169" s="10">
         <v>330</v>
@@ -23291,7 +24986,7 @@
         <v>さらさら純米 打上花火 fireworks</v>
       </c>
       <c r="E170" s="8" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="F170" s="8" t="s">
         <v>775</v>
@@ -23300,7 +24995,7 @@
         <v>789</v>
       </c>
       <c r="H170" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I170" s="9"/>
       <c r="J170" s="22">
@@ -23310,14 +25005,14 @@
         <v>3.6</v>
       </c>
       <c r="L170" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M170" s="18"/>
       <c r="N170" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O170" s="11" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="P170" s="10">
         <v>310</v>
@@ -23353,7 +25048,7 @@
         <v>純米吟醸55 青ラベル 山田錦</v>
       </c>
       <c r="E171" s="8" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="F171" s="8" t="s">
         <v>775</v>
@@ -23362,7 +25057,7 @@
         <v>789</v>
       </c>
       <c r="H171" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I171" s="9"/>
       <c r="J171" s="22">
@@ -23372,14 +25067,14 @@
         <v>3.7</v>
       </c>
       <c r="L171" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M171" s="18"/>
       <c r="N171" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O171" s="11" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="P171" s="10"/>
       <c r="Q171" s="8"/>
@@ -23428,7 +25123,7 @@
         <v>3.6</v>
       </c>
       <c r="L172" s="10" t="s">
-        <v>1257</v>
+        <v>1245</v>
       </c>
       <c r="M172" s="18"/>
       <c r="N172" s="46" t="s">
@@ -23484,7 +25179,7 @@
         <v>3.6</v>
       </c>
       <c r="L173" s="10" t="s">
-        <v>1257</v>
+        <v>1245</v>
       </c>
       <c r="M173" s="18"/>
       <c r="N173" s="46" t="s">
@@ -23540,7 +25235,7 @@
         <v>3.6</v>
       </c>
       <c r="L174" s="10" t="s">
-        <v>1257</v>
+        <v>1245</v>
       </c>
       <c r="M174" s="18"/>
       <c r="N174" s="46" t="s">
@@ -23596,7 +25291,7 @@
         <v>3.7</v>
       </c>
       <c r="L175" s="10" t="s">
-        <v>1257</v>
+        <v>1245</v>
       </c>
       <c r="M175" s="18"/>
       <c r="N175" s="46" t="s">
@@ -23645,7 +25340,7 @@
         <v>801</v>
       </c>
       <c r="I176" s="15" t="s">
-        <v>1355</v>
+        <v>1340</v>
       </c>
       <c r="J176" s="22">
         <v>4</v>
@@ -23655,13 +25350,13 @@
       </c>
       <c r="L176" s="10"/>
       <c r="M176" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N176" s="8" t="s">
         <v>1155</v>
       </c>
       <c r="O176" s="11" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="P176" s="10"/>
       <c r="Q176" s="8"/>
@@ -23703,7 +25398,7 @@
         <v>801</v>
       </c>
       <c r="I177" s="47" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="J177" s="22">
         <v>4</v>
@@ -23713,10 +25408,10 @@
       </c>
       <c r="L177" s="10"/>
       <c r="M177" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N177" s="8" t="s">
-        <v>1222</v>
+        <v>1210</v>
       </c>
       <c r="O177" s="11" t="s">
         <v>870</v>
@@ -23732,10 +25427,10 @@
       </c>
       <c r="S177" s="9"/>
       <c r="T177" s="53" t="s">
-        <v>1351</v>
+        <v>1337</v>
       </c>
       <c r="U177" s="39" t="s">
-        <v>1352</v>
+        <v>1338</v>
       </c>
       <c r="V177" s="8"/>
       <c r="W177" s="8"/>
@@ -23779,10 +25474,10 @@
       </c>
       <c r="L178" s="10"/>
       <c r="M178" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N178" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O178" s="11" t="s">
         <v>870</v>
@@ -23797,7 +25492,7 @@
         <v>790</v>
       </c>
       <c r="S178" s="15" t="s">
-        <v>1264</v>
+        <v>1252</v>
       </c>
       <c r="T178" s="8"/>
       <c r="U178" s="8"/>
@@ -23832,7 +25527,7 @@
         <v>991</v>
       </c>
       <c r="H179" s="12" t="s">
-        <v>1223</v>
+        <v>1211</v>
       </c>
       <c r="I179" s="9"/>
       <c r="J179" s="22">
@@ -23842,11 +25537,11 @@
         <v>3.6</v>
       </c>
       <c r="L179" s="10" t="s">
-        <v>1257</v>
+        <v>1245</v>
       </c>
       <c r="M179" s="18"/>
       <c r="N179" s="46" t="s">
-        <v>1222</v>
+        <v>1210</v>
       </c>
       <c r="O179" s="11" t="s">
         <v>870</v>
@@ -23879,7 +25574,7 @@
         <v>純米吟釀 朝日</v>
       </c>
       <c r="E180" s="8" t="s">
-        <v>1226</v>
+        <v>1214</v>
       </c>
       <c r="F180" s="8" t="s">
         <v>788</v>
@@ -23899,13 +25594,13 @@
       </c>
       <c r="L180" s="10"/>
       <c r="M180" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N180" s="8" t="s">
-        <v>1239</v>
+        <v>1227</v>
       </c>
       <c r="O180" s="8" t="s">
-        <v>1226</v>
+        <v>1214</v>
       </c>
       <c r="P180" s="10">
         <v>1180</v>
@@ -23961,13 +25656,13 @@
       </c>
       <c r="L181" s="10"/>
       <c r="M181" s="18" t="s">
-        <v>1281</v>
+        <v>1269</v>
       </c>
       <c r="N181" s="8" t="s">
-        <v>1275</v>
+        <v>1263</v>
       </c>
       <c r="O181" s="8" t="s">
-        <v>1221</v>
+        <v>1209</v>
       </c>
       <c r="P181" s="10"/>
       <c r="Q181" s="8"/>
@@ -24017,10 +25712,10 @@
       </c>
       <c r="L182" s="10"/>
       <c r="M182" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N182" s="8" t="s">
-        <v>1240</v>
+        <v>1228</v>
       </c>
       <c r="O182" s="11" t="s">
         <v>1003</v>
@@ -24081,19 +25776,19 @@
       </c>
       <c r="L183" s="10"/>
       <c r="M183" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N183" s="39" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
       <c r="O183" s="8" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="P183" s="10">
         <v>179</v>
       </c>
       <c r="Q183" s="8" t="s">
-        <v>1290</v>
+        <v>1278</v>
       </c>
       <c r="R183" s="8" t="s">
         <v>790</v>
@@ -24123,7 +25818,7 @@
         <v>純米吟釀 LED</v>
       </c>
       <c r="E184" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="F184" s="8" t="s">
         <v>788</v>
@@ -24143,13 +25838,13 @@
       </c>
       <c r="L184" s="10"/>
       <c r="M184" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N184" s="8" t="s">
         <v>1152</v>
       </c>
       <c r="O184" s="8" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="P184" s="10">
         <v>1180</v>
@@ -24205,10 +25900,10 @@
       </c>
       <c r="L185" s="10"/>
       <c r="M185" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N185" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O185" s="8" t="s">
         <v>1003</v>
@@ -24223,7 +25918,7 @@
         <v>790</v>
       </c>
       <c r="S185" s="67" t="s">
-        <v>1284</v>
+        <v>1272</v>
       </c>
       <c r="T185" s="8"/>
       <c r="U185" s="8"/>
@@ -24258,7 +25953,7 @@
         <v>776</v>
       </c>
       <c r="H186" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I186" s="9"/>
       <c r="J186" s="22">
@@ -24269,10 +25964,10 @@
       </c>
       <c r="L186" s="10"/>
       <c r="M186" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N186" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O186" s="8" t="s">
         <v>1003</v>
@@ -24287,7 +25982,7 @@
         <v>794</v>
       </c>
       <c r="S186" s="62" t="s">
-        <v>1283</v>
+        <v>1271</v>
       </c>
       <c r="T186" s="8"/>
       <c r="U186" s="8"/>
@@ -24322,7 +26017,7 @@
         <v>776</v>
       </c>
       <c r="H187" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I187" s="9"/>
       <c r="J187" s="22">
@@ -24333,10 +26028,10 @@
       </c>
       <c r="L187" s="10"/>
       <c r="M187" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N187" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O187" s="8" t="s">
         <v>1003</v>
@@ -24351,7 +26046,7 @@
         <v>794</v>
       </c>
       <c r="S187" s="62" t="s">
-        <v>1283</v>
+        <v>1271</v>
       </c>
       <c r="T187" s="8"/>
       <c r="U187" s="8"/>
@@ -24397,13 +26092,13 @@
       </c>
       <c r="L188" s="10"/>
       <c r="M188" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N188" s="39" t="s">
         <v>1156</v>
       </c>
       <c r="O188" s="8" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="P188" s="10"/>
       <c r="Q188" s="8"/>
@@ -24452,14 +26147,14 @@
         <v>4</v>
       </c>
       <c r="L189" s="10" t="s">
-        <v>1260</v>
+        <v>1248</v>
       </c>
       <c r="M189" s="18"/>
       <c r="N189" s="51" t="s">
         <v>1145</v>
       </c>
       <c r="O189" s="8" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="P189" s="10">
         <v>600</v>
@@ -24471,7 +26166,7 @@
         <v>866</v>
       </c>
       <c r="S189" s="15" t="s">
-        <v>1289</v>
+        <v>1277</v>
       </c>
       <c r="T189" s="8"/>
       <c r="U189" s="8"/>
@@ -24517,7 +26212,7 @@
       </c>
       <c r="L190" s="10"/>
       <c r="M190" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N190" s="46" t="s">
         <v>992</v>
@@ -24560,7 +26255,7 @@
         <v>789</v>
       </c>
       <c r="H191" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I191" s="9"/>
       <c r="J191" s="22">
@@ -24570,14 +26265,14 @@
         <v>3.8</v>
       </c>
       <c r="L191" s="10" t="s">
-        <v>1257</v>
+        <v>1245</v>
       </c>
       <c r="M191" s="18"/>
       <c r="N191" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O191" s="8" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="P191" s="10">
         <v>320</v>
@@ -24613,7 +26308,7 @@
         <v>純米吟釀 夏の潮 金魚ラベル</v>
       </c>
       <c r="E192" s="8" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="F192" s="8" t="s">
         <v>775</v>
@@ -24622,7 +26317,7 @@
         <v>789</v>
       </c>
       <c r="H192" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I192" s="9"/>
       <c r="J192" s="22">
@@ -24632,14 +26327,14 @@
         <v>3.8</v>
       </c>
       <c r="L192" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M192" s="18"/>
       <c r="N192" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O192" s="8" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="P192" s="10">
         <v>350</v>
@@ -24684,9 +26379,11 @@
         <v>776</v>
       </c>
       <c r="H193" s="9" t="s">
-        <v>1173</v>
-      </c>
-      <c r="I193" s="9"/>
+        <v>1171</v>
+      </c>
+      <c r="I193" s="64" t="s">
+        <v>1432</v>
+      </c>
       <c r="J193" s="22">
         <v>3.6</v>
       </c>
@@ -24694,11 +26391,11 @@
         <v>3.8</v>
       </c>
       <c r="L193" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M193" s="18"/>
       <c r="N193" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O193" s="8" t="s">
         <v>1161</v>
@@ -24713,10 +26410,14 @@
         <v>794</v>
       </c>
       <c r="S193" s="47" t="s">
-        <v>1282</v>
-      </c>
-      <c r="T193" s="8"/>
-      <c r="U193" s="8"/>
+        <v>1270</v>
+      </c>
+      <c r="T193" s="53" t="s">
+        <v>1430</v>
+      </c>
+      <c r="U193" s="53" t="s">
+        <v>1431</v>
+      </c>
       <c r="V193" s="8"/>
       <c r="W193" s="8"/>
       <c r="X193" s="11"/>
@@ -24748,9 +26449,11 @@
         <v>776</v>
       </c>
       <c r="H194" s="9" t="s">
-        <v>1173</v>
-      </c>
-      <c r="I194" s="9"/>
+        <v>1171</v>
+      </c>
+      <c r="I194" s="64" t="s">
+        <v>1439</v>
+      </c>
       <c r="J194" s="22">
         <v>3.6</v>
       </c>
@@ -24758,11 +26461,11 @@
         <v>3.6</v>
       </c>
       <c r="L194" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M194" s="18"/>
       <c r="N194" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O194" s="8" t="s">
         <v>1161</v>
@@ -24777,10 +26480,14 @@
         <v>794</v>
       </c>
       <c r="S194" s="47" t="s">
-        <v>1282</v>
-      </c>
-      <c r="T194" s="8"/>
-      <c r="U194" s="8"/>
+        <v>1270</v>
+      </c>
+      <c r="T194" s="51" t="s">
+        <v>1433</v>
+      </c>
+      <c r="U194" s="51" t="s">
+        <v>1434</v>
+      </c>
       <c r="V194" s="8"/>
       <c r="W194" s="8"/>
       <c r="X194" s="11"/>
@@ -24812,9 +26519,11 @@
         <v>776</v>
       </c>
       <c r="H195" s="9" t="s">
-        <v>1173</v>
-      </c>
-      <c r="I195" s="9"/>
+        <v>1171</v>
+      </c>
+      <c r="I195" s="64" t="s">
+        <v>1440</v>
+      </c>
       <c r="J195" s="22">
         <v>4</v>
       </c>
@@ -24822,11 +26531,11 @@
         <v>4</v>
       </c>
       <c r="L195" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M195" s="18"/>
       <c r="N195" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O195" s="8" t="s">
         <v>1161</v>
@@ -24841,10 +26550,14 @@
         <v>794</v>
       </c>
       <c r="S195" s="47" t="s">
-        <v>1282</v>
-      </c>
-      <c r="T195" s="8"/>
-      <c r="U195" s="8"/>
+        <v>1270</v>
+      </c>
+      <c r="T195" s="51" t="s">
+        <v>1435</v>
+      </c>
+      <c r="U195" s="51" t="s">
+        <v>1436</v>
+      </c>
       <c r="V195" s="8"/>
       <c r="W195" s="8"/>
       <c r="X195" s="11"/>
@@ -24876,9 +26589,11 @@
         <v>776</v>
       </c>
       <c r="H196" s="9" t="s">
-        <v>1173</v>
-      </c>
-      <c r="I196" s="9"/>
+        <v>1171</v>
+      </c>
+      <c r="I196" s="64" t="s">
+        <v>1441</v>
+      </c>
       <c r="J196" s="22">
         <v>3.8</v>
       </c>
@@ -24886,11 +26601,11 @@
         <v>4</v>
       </c>
       <c r="L196" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M196" s="18"/>
       <c r="N196" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O196" s="8" t="s">
         <v>1161</v>
@@ -24905,10 +26620,14 @@
         <v>794</v>
       </c>
       <c r="S196" s="47" t="s">
-        <v>1282</v>
-      </c>
-      <c r="T196" s="8"/>
-      <c r="U196" s="8"/>
+        <v>1270</v>
+      </c>
+      <c r="T196" s="51" t="s">
+        <v>1437</v>
+      </c>
+      <c r="U196" s="46" t="s">
+        <v>1438</v>
+      </c>
       <c r="V196" s="8"/>
       <c r="W196" s="8"/>
       <c r="X196" s="11"/>
@@ -24940,9 +26659,11 @@
         <v>776</v>
       </c>
       <c r="H197" s="9" t="s">
-        <v>1173</v>
-      </c>
-      <c r="I197" s="9"/>
+        <v>1171</v>
+      </c>
+      <c r="I197" s="64" t="s">
+        <v>1444</v>
+      </c>
       <c r="J197" s="22">
         <v>4</v>
       </c>
@@ -24950,11 +26671,11 @@
         <v>4</v>
       </c>
       <c r="L197" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M197" s="18"/>
       <c r="N197" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O197" s="8" t="s">
         <v>1161</v>
@@ -24969,10 +26690,14 @@
         <v>794</v>
       </c>
       <c r="S197" s="47" t="s">
-        <v>1282</v>
-      </c>
-      <c r="T197" s="8"/>
-      <c r="U197" s="8"/>
+        <v>1270</v>
+      </c>
+      <c r="T197" s="53" t="s">
+        <v>1442</v>
+      </c>
+      <c r="U197" s="51" t="s">
+        <v>1443</v>
+      </c>
       <c r="V197" s="8"/>
       <c r="W197" s="8"/>
       <c r="X197" s="11"/>
@@ -25004,9 +26729,11 @@
         <v>776</v>
       </c>
       <c r="H198" s="9" t="s">
-        <v>1173</v>
-      </c>
-      <c r="I198" s="9"/>
+        <v>1171</v>
+      </c>
+      <c r="I198" s="64" t="s">
+        <v>1447</v>
+      </c>
       <c r="J198" s="22">
         <v>4</v>
       </c>
@@ -25014,11 +26741,11 @@
         <v>4</v>
       </c>
       <c r="L198" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M198" s="18"/>
       <c r="N198" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O198" s="8" t="s">
         <v>1161</v>
@@ -25033,10 +26760,14 @@
         <v>794</v>
       </c>
       <c r="S198" s="47" t="s">
-        <v>1282</v>
-      </c>
-      <c r="T198" s="8"/>
-      <c r="U198" s="8"/>
+        <v>1270</v>
+      </c>
+      <c r="T198" s="53" t="s">
+        <v>1445</v>
+      </c>
+      <c r="U198" s="46" t="s">
+        <v>1446</v>
+      </c>
       <c r="V198" s="8"/>
       <c r="W198" s="8"/>
       <c r="X198" s="11"/>
@@ -25068,9 +26799,11 @@
         <v>776</v>
       </c>
       <c r="H199" s="9" t="s">
-        <v>1173</v>
-      </c>
-      <c r="I199" s="9"/>
+        <v>1171</v>
+      </c>
+      <c r="I199" s="64" t="s">
+        <v>1450</v>
+      </c>
       <c r="J199" s="22">
         <v>3.8</v>
       </c>
@@ -25078,11 +26811,11 @@
         <v>4</v>
       </c>
       <c r="L199" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M199" s="18"/>
       <c r="N199" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O199" s="8" t="s">
         <v>1161</v>
@@ -25097,10 +26830,14 @@
         <v>794</v>
       </c>
       <c r="S199" s="47" t="s">
-        <v>1282</v>
-      </c>
-      <c r="T199" s="8"/>
-      <c r="U199" s="8"/>
+        <v>1270</v>
+      </c>
+      <c r="T199" s="51" t="s">
+        <v>1448</v>
+      </c>
+      <c r="U199" s="51" t="s">
+        <v>1449</v>
+      </c>
       <c r="V199" s="8"/>
       <c r="W199" s="8"/>
       <c r="X199" s="11"/>
@@ -25132,9 +26869,11 @@
         <v>776</v>
       </c>
       <c r="H200" s="9" t="s">
-        <v>1173</v>
-      </c>
-      <c r="I200" s="9"/>
+        <v>1171</v>
+      </c>
+      <c r="I200" s="64" t="s">
+        <v>1453</v>
+      </c>
       <c r="J200" s="22">
         <v>4.0999999999999996</v>
       </c>
@@ -25142,11 +26881,11 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="L200" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M200" s="18"/>
       <c r="N200" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O200" s="8" t="s">
         <v>1161</v>
@@ -25161,10 +26900,14 @@
         <v>794</v>
       </c>
       <c r="S200" s="47" t="s">
-        <v>1282</v>
-      </c>
-      <c r="T200" s="8"/>
-      <c r="U200" s="8"/>
+        <v>1270</v>
+      </c>
+      <c r="T200" s="51" t="s">
+        <v>1451</v>
+      </c>
+      <c r="U200" s="51" t="s">
+        <v>1452</v>
+      </c>
       <c r="V200" s="8"/>
       <c r="W200" s="8"/>
       <c r="X200" s="11"/>
@@ -25198,7 +26941,9 @@
       <c r="H201" s="28" t="s">
         <v>801</v>
       </c>
-      <c r="I201" s="9"/>
+      <c r="I201" s="64" t="s">
+        <v>1429</v>
+      </c>
       <c r="J201" s="22">
         <v>3.2</v>
       </c>
@@ -25207,10 +26952,10 @@
       </c>
       <c r="L201" s="10"/>
       <c r="M201" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N201" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O201" s="8" t="s">
         <v>1161</v>
@@ -25227,8 +26972,12 @@
       <c r="S201" s="63" t="s">
         <v>1165</v>
       </c>
-      <c r="T201" s="8"/>
-      <c r="U201" s="8"/>
+      <c r="T201" s="53" t="s">
+        <v>1427</v>
+      </c>
+      <c r="U201" s="53" t="s">
+        <v>1428</v>
+      </c>
       <c r="V201" s="8"/>
       <c r="W201" s="8"/>
       <c r="X201" s="11"/>
@@ -25262,7 +27011,9 @@
       <c r="H202" s="28" t="s">
         <v>801</v>
       </c>
-      <c r="I202" s="9"/>
+      <c r="I202" s="64" t="s">
+        <v>1425</v>
+      </c>
       <c r="J202" s="22">
         <v>3.7</v>
       </c>
@@ -25271,10 +27022,10 @@
       </c>
       <c r="L202" s="10"/>
       <c r="M202" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N202" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O202" s="8" t="s">
         <v>1161</v>
@@ -25291,8 +27042,12 @@
       <c r="S202" s="63" t="s">
         <v>1165</v>
       </c>
-      <c r="T202" s="8"/>
-      <c r="U202" s="8"/>
+      <c r="T202" s="51" t="s">
+        <v>1424</v>
+      </c>
+      <c r="U202" s="51" t="s">
+        <v>1426</v>
+      </c>
       <c r="V202" s="8"/>
       <c r="W202" s="8"/>
       <c r="X202" s="11"/>
@@ -25326,7 +27081,9 @@
       <c r="H203" s="28" t="s">
         <v>801</v>
       </c>
-      <c r="I203" s="9"/>
+      <c r="I203" s="77" t="s">
+        <v>1423</v>
+      </c>
       <c r="J203" s="22">
         <v>3.5</v>
       </c>
@@ -25335,7 +27092,7 @@
       </c>
       <c r="L203" s="10"/>
       <c r="M203" s="18" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N203" s="9"/>
       <c r="O203" s="8" t="s">
@@ -25351,8 +27108,12 @@
         <v>790</v>
       </c>
       <c r="S203" s="9"/>
-      <c r="T203" s="8"/>
-      <c r="U203" s="8"/>
+      <c r="T203" s="53" t="s">
+        <v>1421</v>
+      </c>
+      <c r="U203" s="53" t="s">
+        <v>1422</v>
+      </c>
       <c r="V203" s="8"/>
       <c r="W203" s="8"/>
       <c r="X203" s="11"/>
@@ -25375,7 +27136,7 @@
         <v>銀黑 金紋錦 無濾過生原酒</v>
       </c>
       <c r="E204" s="8" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="F204" s="8" t="s">
         <v>775</v>
@@ -25394,14 +27155,14 @@
         <v>4</v>
       </c>
       <c r="L204" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M204" s="18"/>
       <c r="N204" s="51" t="s">
-        <v>1274</v>
+        <v>1262</v>
       </c>
       <c r="O204" s="8" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="P204" s="10"/>
       <c r="Q204" s="8"/>
@@ -25442,7 +27203,9 @@
       <c r="H205" s="56" t="s">
         <v>801</v>
       </c>
-      <c r="I205" s="57"/>
+      <c r="I205" s="75" t="s">
+        <v>1417</v>
+      </c>
       <c r="J205" s="58">
         <v>3.8</v>
       </c>
@@ -25451,10 +27214,10 @@
       </c>
       <c r="L205" s="10"/>
       <c r="M205" s="60" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N205" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O205" s="61" t="s">
         <v>1161</v>
@@ -25471,8 +27234,12 @@
       <c r="S205" s="63" t="s">
         <v>1165</v>
       </c>
-      <c r="T205" s="55"/>
-      <c r="U205" s="55"/>
+      <c r="T205" s="70" t="s">
+        <v>1415</v>
+      </c>
+      <c r="U205" s="70" t="s">
+        <v>1415</v>
+      </c>
       <c r="V205" s="55"/>
       <c r="W205" s="55"/>
       <c r="X205" s="61"/>
@@ -25481,10 +27248,10 @@
     </row>
     <row r="206" spans="1:26" s="69" customFormat="1" ht="24.95" customHeight="1">
       <c r="A206" s="55" t="s">
-        <v>1218</v>
+        <v>1207</v>
       </c>
       <c r="B206" s="55" t="s">
-        <v>1217</v>
+        <v>1206</v>
       </c>
       <c r="C206" s="55" t="str">
         <f>IF(B206="","",IFERROR(INDEX(SakesV5[銘柄],MATCH(B206,SakesV5[酒款ID],0)),"酒款ID未找到"))</f>
@@ -25504,9 +27271,11 @@
         <v>789</v>
       </c>
       <c r="H206" s="57" t="s">
-        <v>1173</v>
-      </c>
-      <c r="I206" s="57"/>
+        <v>1171</v>
+      </c>
+      <c r="I206" s="75" t="s">
+        <v>1420</v>
+      </c>
       <c r="J206" s="58">
         <v>3.8</v>
       </c>
@@ -25515,10 +27284,10 @@
       </c>
       <c r="L206" s="59"/>
       <c r="M206" s="60" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N206" s="57" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O206" s="61" t="s">
         <v>1166</v>
@@ -25535,8 +27304,12 @@
       <c r="S206" s="63" t="s">
         <v>1160</v>
       </c>
-      <c r="T206" s="55"/>
-      <c r="U206" s="55"/>
+      <c r="T206" s="76" t="s">
+        <v>1418</v>
+      </c>
+      <c r="U206" s="76" t="s">
+        <v>1419</v>
+      </c>
       <c r="V206" s="55"/>
       <c r="W206" s="55"/>
       <c r="X206" s="61"/>
@@ -25545,7 +27318,7 @@
     </row>
     <row r="207" spans="1:26" s="69" customFormat="1" ht="48.75" customHeight="1">
       <c r="A207" s="55" t="s">
-        <v>1244</v>
+        <v>1232</v>
       </c>
       <c r="B207" s="55" t="s">
         <v>355</v>
@@ -25559,7 +27332,7 @@
         <v>寵深花風</v>
       </c>
       <c r="E207" s="55" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="F207" s="55" t="s">
         <v>775</v>
@@ -25570,8 +27343,8 @@
       <c r="H207" s="53" t="s">
         <v>1157</v>
       </c>
-      <c r="I207" s="71" t="s">
-        <v>1318</v>
+      <c r="I207" s="74" t="s">
+        <v>1372</v>
       </c>
       <c r="J207" s="58">
         <v>4.5</v>
@@ -25580,14 +27353,14 @@
         <v>4.5</v>
       </c>
       <c r="L207" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M207" s="60"/>
       <c r="N207" s="27" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
       <c r="O207" s="61" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P207" s="59">
         <v>800</v>
@@ -25600,10 +27373,10 @@
       </c>
       <c r="S207" s="57"/>
       <c r="T207" s="70" t="s">
-        <v>1305</v>
+        <v>1293</v>
       </c>
       <c r="U207" s="42" t="s">
-        <v>1306</v>
+        <v>1416</v>
       </c>
       <c r="V207" s="55"/>
       <c r="W207" s="55"/>
@@ -25613,10 +27386,10 @@
     </row>
     <row r="208" spans="1:26" s="62" customFormat="1" ht="24.95" customHeight="1">
       <c r="A208" s="55" t="s">
-        <v>1261</v>
+        <v>1249</v>
       </c>
       <c r="B208" s="55" t="s">
-        <v>1271</v>
+        <v>1259</v>
       </c>
       <c r="C208" s="55" t="str">
         <f>IF(B208="","",IFERROR(INDEX(SakesV5[銘柄],MATCH(B208,SakesV5[酒款ID],0)),"酒款ID未找到"))</f>
@@ -25627,7 +27400,7 @@
         <v>2024 R-type</v>
       </c>
       <c r="E208" s="55" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="F208" s="55" t="s">
         <v>788</v>
@@ -25636,7 +27409,7 @@
         <v>789</v>
       </c>
       <c r="H208" s="57" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I208" s="57"/>
       <c r="J208" s="58">
@@ -25647,13 +27420,13 @@
       </c>
       <c r="L208" s="59"/>
       <c r="M208" s="60" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="N208" s="57" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O208" s="61" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="P208" s="59">
         <v>8000</v>
@@ -25677,10 +27450,10 @@
     </row>
     <row r="209" spans="1:26" s="69" customFormat="1" ht="48" customHeight="1">
       <c r="A209" s="55" t="s">
-        <v>1262</v>
+        <v>1250</v>
       </c>
       <c r="B209" s="55" t="s">
-        <v>1285</v>
+        <v>1273</v>
       </c>
       <c r="C209" s="55" t="str">
         <f>IF(B209="","",IFERROR(INDEX(SakesV5[銘柄],MATCH(B209,SakesV5[酒款ID],0)),"酒款ID未找到"))</f>
@@ -25700,7 +27473,7 @@
         <v>776</v>
       </c>
       <c r="H209" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="I209" s="57"/>
       <c r="J209" s="58">
@@ -25710,14 +27483,14 @@
         <v>3.8</v>
       </c>
       <c r="L209" s="10" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="M209" s="60"/>
       <c r="N209" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="O209" s="8" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="P209" s="59">
         <v>1580</v>
@@ -25729,7 +27502,7 @@
         <v>794</v>
       </c>
       <c r="S209" s="62" t="s">
-        <v>1283</v>
+        <v>1271</v>
       </c>
       <c r="T209" s="55"/>
       <c r="U209" s="55"/>
@@ -35091,14 +36864,14 @@
     </row>
   </sheetData>
   <phoneticPr fontId="20" type="noConversion"/>
+  <conditionalFormatting sqref="A2:A484">
+    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C2:D484">
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="酒款ID未找到"/>
+    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="酒款ID未找到"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N176">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="酒款ID未找到"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A484">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="酒款ID未找到"/>
   </conditionalFormatting>
   <dataValidations count="7">
     <dataValidation type="list" sqref="H91:H94 H84:H89 H207 G2:G484" xr:uid="{00000000-0002-0000-0100-000000000000}">
